--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6CB11A-D801-4F43-B3C5-97E0265E3CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D91CE65A-957A-4420-8032-2530016C8C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Level_3" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -182,7 +183,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -389,6 +390,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -637,7 +644,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -654,6 +661,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6233,6 +6243,21 @@
       <c r="BS64" s="3">
         <v>6</v>
       </c>
+      <c r="BV64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BW64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BX64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BY64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BZ64" s="6">
+        <v>12</v>
+      </c>
       <c r="DB64" s="1">
         <v>2</v>
       </c>
@@ -8194,6 +8219,21 @@
       </c>
       <c r="BS85" s="3">
         <v>6</v>
+      </c>
+      <c r="BV85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BW85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BX85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BY85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BZ85" s="6">
+        <v>12</v>
       </c>
       <c r="CT85" s="1">
         <v>3</v>

--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D91CE65A-957A-4420-8032-2530016C8C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2256638-63B1-458D-82C7-8A3A60ED8186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Level_3" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -6243,21 +6242,6 @@
       <c r="BS64" s="3">
         <v>6</v>
       </c>
-      <c r="BV64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BW64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BX64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BY64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BZ64" s="6">
-        <v>12</v>
-      </c>
       <c r="DB64" s="1">
         <v>2</v>
       </c>
@@ -6287,38 +6271,38 @@
       <c r="BR65" s="2">
         <v>0</v>
       </c>
-      <c r="BS65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY65" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ65" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA65" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB65" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC65" s="2">
-        <v>0</v>
+      <c r="BS65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BX65" s="6">
+        <v>12</v>
+      </c>
+      <c r="BY65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BZ65" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA65" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB65" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC65" s="6">
+        <v>12</v>
       </c>
       <c r="CD65" s="2">
         <v>0</v>
@@ -8128,38 +8112,38 @@
       <c r="BR84" s="2">
         <v>0</v>
       </c>
-      <c r="BS84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC84" s="2">
-        <v>0</v>
+      <c r="BS84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BX84" s="6">
+        <v>12</v>
+      </c>
+      <c r="BY84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BZ84" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA84" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB84" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC84" s="6">
+        <v>12</v>
       </c>
       <c r="CD84" s="2">
         <v>0</v>
@@ -8219,21 +8203,6 @@
       </c>
       <c r="BS85" s="3">
         <v>6</v>
-      </c>
-      <c r="BV85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BW85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BX85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BY85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BZ85" s="6">
-        <v>12</v>
       </c>
       <c r="CT85" s="1">
         <v>3</v>

--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2256638-63B1-458D-82C7-8A3A60ED8186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35E2CD8-0E93-441C-8128-3ED05E4041A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -8898,7 +8898,7 @@
         <v>2</v>
       </c>
       <c r="DF100" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DN100" s="1">
         <v>2</v>
@@ -9064,7 +9064,7 @@
         <v>0</v>
       </c>
       <c r="DL102" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DN102" s="1">
         <v>0</v>
@@ -9123,7 +9123,7 @@
         <v>2</v>
       </c>
       <c r="DI103" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DK103" s="1">
         <v>0</v>

--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35E2CD8-0E93-441C-8128-3ED05E4041A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A488F924-3315-4084-B93A-85508C66D695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1" s="1">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1" s="1">
         <v>0</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1" s="1">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="Q1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1" s="1">
         <v>0</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="T1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U1" s="1">
         <v>0</v>
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="W1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X1" s="1">
         <v>0</v>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="Z1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA1" s="1">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="AC1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD1" s="1">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="AF1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG1" s="1">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="AI1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ1" s="1">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="AL1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM1" s="1">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="AO1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP1" s="1">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="AR1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS1" s="1">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="AU1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV1" s="1">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="AX1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY1" s="1">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="BA1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB1" s="1">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="BD1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE1" s="1">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="BG1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH1" s="1">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="BJ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK1" s="1">
         <v>0</v>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="BM1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN1" s="1">
         <v>0</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="BP1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ1" s="1">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="BS1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT1" s="1">
         <v>0</v>
@@ -1269,16 +1269,16 @@
         <v>0</v>
       </c>
       <c r="BV1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW1" s="1">
         <v>0</v>
       </c>
       <c r="BX1" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BY1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ1" s="1">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="CB1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC1" s="1">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="CE1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF1" s="1">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="CH1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI1" s="1">
         <v>0</v>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="CK1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL1" s="1">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="CN1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO1" s="1">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="CQ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR1" s="1">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="CT1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU1" s="1">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="CW1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX1" s="1">
         <v>0</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="CZ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA1" s="1">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="DC1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD1" s="1">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="DF1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG1" s="1">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="DI1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ1" s="1">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="DL1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM1" s="1">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="DO1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP1" s="1">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="DR1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS1" s="1">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="DU1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV1" s="1">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="DX1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY1" s="1">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="EA1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB1" s="1">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="ED1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE1" s="1">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="EG1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH1" s="1">
         <v>0</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="EJ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK1" s="1">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="EM1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN1" s="1">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="ET8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:150" x14ac:dyDescent="0.45">
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="ET11" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:150" x14ac:dyDescent="0.45">
@@ -2825,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="ET14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:150" x14ac:dyDescent="0.45">
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="ET17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:150" x14ac:dyDescent="0.45">
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="ET20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:150" x14ac:dyDescent="0.45">
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="ET23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:150" x14ac:dyDescent="0.45">
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="ET26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:150" x14ac:dyDescent="0.45">
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="ET29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:150" x14ac:dyDescent="0.45">
@@ -3917,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="ET32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:150" x14ac:dyDescent="0.45">
@@ -4058,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="ET35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:150" x14ac:dyDescent="0.45">
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="ET38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:150" x14ac:dyDescent="0.45">
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="ET41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:150" x14ac:dyDescent="0.45">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="ET44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:150" x14ac:dyDescent="0.45">
@@ -4856,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="ET47" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:150" x14ac:dyDescent="0.45">
@@ -5132,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="ET50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:150" x14ac:dyDescent="0.45">
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="ET53" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:150" x14ac:dyDescent="0.45">
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="ET56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:150" x14ac:dyDescent="0.45">
@@ -5966,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="ET59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:150" x14ac:dyDescent="0.45">
@@ -6197,7 +6197,7 @@
         <v>0</v>
       </c>
       <c r="ET62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:150" x14ac:dyDescent="0.45">
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="ET65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:150" x14ac:dyDescent="0.45">
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="ET68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:150" x14ac:dyDescent="0.45">
@@ -6887,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="ET71" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:150" x14ac:dyDescent="0.45">
@@ -7145,12 +7145,12 @@
         <v>0</v>
       </c>
       <c r="ET74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B75" s="1">
         <v>0</v>
@@ -7450,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="ET75" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:150" x14ac:dyDescent="0.45">
@@ -7604,7 +7604,7 @@
         <v>2</v>
       </c>
       <c r="ET77" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:150" x14ac:dyDescent="0.45">
@@ -7835,7 +7835,7 @@
         <v>2</v>
       </c>
       <c r="ET80" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:150" x14ac:dyDescent="0.45">
@@ -8075,7 +8075,7 @@
         <v>2</v>
       </c>
       <c r="ET83" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:150" x14ac:dyDescent="0.45">
@@ -8306,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="ET86" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:150" x14ac:dyDescent="0.45">
@@ -8474,7 +8474,7 @@
         <v>0</v>
       </c>
       <c r="ET89" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:150" x14ac:dyDescent="0.45">
@@ -8594,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="ET92" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:150" x14ac:dyDescent="0.45">
@@ -8723,7 +8723,7 @@
         <v>0</v>
       </c>
       <c r="ET95" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:150" x14ac:dyDescent="0.45">
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="ET98" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:150" x14ac:dyDescent="0.45">
@@ -9026,7 +9026,7 @@
         <v>0</v>
       </c>
       <c r="ET101" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:150" x14ac:dyDescent="0.45">
@@ -9197,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="ET104" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:150" x14ac:dyDescent="0.45">
@@ -9302,7 +9302,7 @@
         <v>0</v>
       </c>
       <c r="ET107" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:150" x14ac:dyDescent="0.45">
@@ -9392,7 +9392,7 @@
         <v>4</v>
       </c>
       <c r="ET110" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:150" x14ac:dyDescent="0.45">
@@ -9488,7 +9488,7 @@
         <v>4</v>
       </c>
       <c r="ET113" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:150" x14ac:dyDescent="0.45">
@@ -9584,7 +9584,7 @@
         <v>4</v>
       </c>
       <c r="ET116" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:150" x14ac:dyDescent="0.45">
@@ -9770,7 +9770,7 @@
         <v>0</v>
       </c>
       <c r="ET119" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:150" x14ac:dyDescent="0.45">
@@ -9953,7 +9953,7 @@
         <v>4</v>
       </c>
       <c r="ET122" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:150" x14ac:dyDescent="0.45">
@@ -10280,7 +10280,7 @@
         <v>8</v>
       </c>
       <c r="ET125" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:150" x14ac:dyDescent="0.45">
@@ -10709,7 +10709,7 @@
         <v>8</v>
       </c>
       <c r="ET128" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:150" x14ac:dyDescent="0.45">
@@ -11129,7 +11129,7 @@
         <v>8</v>
       </c>
       <c r="ET131" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:150" x14ac:dyDescent="0.45">
@@ -11540,7 +11540,7 @@
         <v>4</v>
       </c>
       <c r="ET134" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:150" x14ac:dyDescent="0.45">
@@ -11990,7 +11990,7 @@
         <v>4</v>
       </c>
       <c r="ET137" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:150" x14ac:dyDescent="0.45">
@@ -12476,7 +12476,7 @@
         <v>4</v>
       </c>
       <c r="ET140" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:150" x14ac:dyDescent="0.45">
@@ -12917,7 +12917,7 @@
         <v>4</v>
       </c>
       <c r="ET143" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:150" x14ac:dyDescent="0.45">
@@ -13111,7 +13111,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
@@ -13120,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" s="1">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" s="1">
         <v>0</v>
@@ -13138,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="Q150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R150" s="1">
         <v>0</v>
@@ -13147,7 +13147,7 @@
         <v>0</v>
       </c>
       <c r="T150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U150" s="1">
         <v>0</v>
@@ -13156,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="W150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X150" s="1">
         <v>0</v>
@@ -13165,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="Z150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA150" s="1">
         <v>0</v>
@@ -13174,7 +13174,7 @@
         <v>0</v>
       </c>
       <c r="AC150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD150" s="1">
         <v>0</v>
@@ -13183,7 +13183,7 @@
         <v>0</v>
       </c>
       <c r="AF150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG150" s="1">
         <v>0</v>
@@ -13192,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ150" s="1">
         <v>0</v>
@@ -13201,7 +13201,7 @@
         <v>0</v>
       </c>
       <c r="AL150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM150" s="1">
         <v>0</v>
@@ -13210,7 +13210,7 @@
         <v>0</v>
       </c>
       <c r="AO150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP150" s="1">
         <v>0</v>
@@ -13219,7 +13219,7 @@
         <v>0</v>
       </c>
       <c r="AR150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS150" s="1">
         <v>0</v>
@@ -13228,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="AU150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV150" s="1">
         <v>0</v>
@@ -13237,7 +13237,7 @@
         <v>0</v>
       </c>
       <c r="AX150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY150" s="1">
         <v>0</v>
@@ -13246,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="BA150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB150" s="1">
         <v>0</v>
@@ -13255,7 +13255,7 @@
         <v>0</v>
       </c>
       <c r="BD150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE150" s="1">
         <v>0</v>
@@ -13264,7 +13264,7 @@
         <v>0</v>
       </c>
       <c r="BG150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH150" s="1">
         <v>0</v>
@@ -13273,7 +13273,7 @@
         <v>0</v>
       </c>
       <c r="BJ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK150" s="1">
         <v>0</v>
@@ -13282,7 +13282,7 @@
         <v>0</v>
       </c>
       <c r="BM150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN150" s="1">
         <v>0</v>
@@ -13291,7 +13291,7 @@
         <v>0</v>
       </c>
       <c r="BP150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ150" s="1">
         <v>0</v>
@@ -13300,7 +13300,7 @@
         <v>0</v>
       </c>
       <c r="BS150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT150" s="1">
         <v>0</v>
@@ -13309,16 +13309,16 @@
         <v>0</v>
       </c>
       <c r="BV150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW150" s="1">
         <v>0</v>
       </c>
       <c r="BX150" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BY150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ150" s="1">
         <v>0</v>
@@ -13327,7 +13327,7 @@
         <v>0</v>
       </c>
       <c r="CB150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC150" s="1">
         <v>0</v>
@@ -13336,7 +13336,7 @@
         <v>0</v>
       </c>
       <c r="CE150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF150" s="1">
         <v>0</v>
@@ -13345,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="CH150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI150" s="1">
         <v>0</v>
@@ -13354,7 +13354,7 @@
         <v>0</v>
       </c>
       <c r="CK150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL150" s="1">
         <v>0</v>
@@ -13363,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="CN150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO150" s="1">
         <v>0</v>
@@ -13372,7 +13372,7 @@
         <v>0</v>
       </c>
       <c r="CQ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR150" s="1">
         <v>0</v>
@@ -13381,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="CT150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU150" s="1">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="CW150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX150" s="1">
         <v>0</v>
@@ -13399,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="CZ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA150" s="1">
         <v>0</v>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="DC150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD150" s="1">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="DF150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG150" s="1">
         <v>0</v>
@@ -13426,7 +13426,7 @@
         <v>0</v>
       </c>
       <c r="DI150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ150" s="1">
         <v>0</v>
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="DL150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM150" s="1">
         <v>0</v>
@@ -13444,7 +13444,7 @@
         <v>0</v>
       </c>
       <c r="DO150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP150" s="1">
         <v>0</v>
@@ -13453,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="DR150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS150" s="1">
         <v>0</v>
@@ -13462,7 +13462,7 @@
         <v>0</v>
       </c>
       <c r="DU150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV150" s="1">
         <v>0</v>
@@ -13471,7 +13471,7 @@
         <v>0</v>
       </c>
       <c r="DX150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY150" s="1">
         <v>0</v>
@@ -13480,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="EA150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB150" s="1">
         <v>0</v>
@@ -13489,7 +13489,7 @@
         <v>0</v>
       </c>
       <c r="ED150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE150" s="1">
         <v>0</v>
@@ -13498,7 +13498,7 @@
         <v>0</v>
       </c>
       <c r="EG150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH150" s="1">
         <v>0</v>
@@ -13507,7 +13507,7 @@
         <v>0</v>
       </c>
       <c r="EJ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK150" s="1">
         <v>0</v>
@@ -13516,7 +13516,7 @@
         <v>0</v>
       </c>
       <c r="EM150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN150" s="1">
         <v>0</v>

--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC597086-B203-45C5-94D9-43A7D44E30AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9EE233-C8D8-4502-BF80-198DBB24D6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="13836" windowHeight="11712" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="2508" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -756,10 +756,10 @@
         <v>8</v>
       </c>
       <c r="CI3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS3" s="1">
         <v>0</v>
@@ -864,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="CI6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV6" s="1">
         <v>0</v>
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="CI9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV9" s="1">
         <v>0</v>
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="CI12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV12" s="1">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>0</v>
       </c>
       <c r="T14" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC14" s="1">
         <v>0</v>
       </c>
       <c r="BZ14" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV14" s="1">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS17" s="1">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="BZ17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV17" s="1">
         <v>0</v>
@@ -1439,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="CI19" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM19" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV19" s="1">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP20" s="1">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="BZ20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI20" s="1">
         <v>0</v>
@@ -1661,10 +1661,10 @@
         <v>0</v>
       </c>
       <c r="CI22" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM22" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ22" s="3">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="T23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM23" s="1">
         <v>0</v>
@@ -1705,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="BZ23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA23" s="3">
         <v>0</v>
@@ -1770,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" s="1">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="CI25" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM25" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ25" s="3">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V26" s="1">
         <v>6</v>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="BZ26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI26" s="1">
         <v>0</v>
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M27" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" s="1">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="BO27" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ27" s="1">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="AE28" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP28" s="3">
         <v>0</v>
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="CI28" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM28" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV28" s="1">
         <v>0</v>
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="BZ29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI29" s="1">
         <v>0</v>
@@ -2253,10 +2253,10 @@
         <v>6</v>
       </c>
       <c r="H30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R30" s="1">
         <v>5</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="BO30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ30" s="1">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="AE31" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP31" s="3">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE32" s="1">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="BZ32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV32" s="1">
         <v>0</v>
@@ -2418,10 +2418,10 @@
         <v>6</v>
       </c>
       <c r="H33" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O33" s="1">
         <v>5</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="BO33" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ33" s="1">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AE34" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH34" s="3">
         <v>0</v>
@@ -2567,10 +2567,10 @@
         <v>0</v>
       </c>
       <c r="CI34" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM34" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV34" s="1">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE35" s="1">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="BZ35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI35" s="1">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="BO36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ36" s="1">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="AE37" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH37" s="3">
         <v>0</v>
@@ -2780,10 +2780,10 @@
         <v>0</v>
       </c>
       <c r="CI37" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM37" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV37" s="1">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE38" s="1">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="BZ38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI38" s="1">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="BO39" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ39" s="1">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="AE40" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO40" s="1">
         <v>0</v>
@@ -2870,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="CI40" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM40" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV40" s="1">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE41" s="1">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="BZ41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI41" s="1">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="BO42" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ42" s="1">
         <v>0</v>
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="AE43" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN43" s="2">
         <v>0</v>
@@ -3146,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="CI43" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM43" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV43" s="1">
         <v>0</v>
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE44" s="1">
         <v>0</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="BZ44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI44" s="1">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="BO45" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ45" s="1">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="AE46" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN46" s="2">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE47" s="1">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="BO48" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV48" s="1">
         <v>0</v>
@@ -3665,10 +3665,10 @@
         <v>5</v>
       </c>
       <c r="H49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O49" s="1">
         <v>6</v>
@@ -3695,7 +3695,7 @@
         <v>5</v>
       </c>
       <c r="AE49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50" s="3">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="BO51" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV51" s="1">
         <v>0</v>
@@ -4037,10 +4037,10 @@
         <v>8</v>
       </c>
       <c r="H52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P52" s="4">
         <v>8</v>
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="AE52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN52" s="2">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U53" s="3">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="BO54" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV54" s="1">
         <v>0</v>
@@ -4334,10 +4334,10 @@
         <v>8</v>
       </c>
       <c r="H55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P55" s="4">
         <v>8</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="AE55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN55" s="2">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE56" s="1">
         <v>0</v>
@@ -4582,13 +4582,13 @@
         <v>0</v>
       </c>
       <c r="BZ56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV56" s="1">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="BO57" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ57" s="1">
         <v>5</v>
@@ -4706,10 +4706,10 @@
         <v>6</v>
       </c>
       <c r="H58" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M58" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O58" s="1">
         <v>5</v>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="AE58" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN58" s="2">
         <v>0</v>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="T59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE59" s="1">
         <v>0</v>
@@ -4888,13 +4888,13 @@
         <v>0</v>
       </c>
       <c r="BZ59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV59" s="1">
         <v>0</v>
@@ -4904,7 +4904,7 @@
       <c r="A60" s="1">
         <v>0</v>
       </c>
-      <c r="H60" s="1">
+      <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="N60" s="1">
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="BO60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ60" s="1">
         <v>0</v>
@@ -4996,7 +4996,7 @@
       <c r="A61" s="1">
         <v>0</v>
       </c>
-      <c r="G61" s="1">
+      <c r="F61" s="1">
         <v>5</v>
       </c>
       <c r="O61" s="1">
@@ -5006,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="AE61" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF61" s="1">
         <v>0</v>
@@ -5037,20 +5037,20 @@
       <c r="A62" s="1">
         <v>0</v>
       </c>
-      <c r="F62" s="1">
+      <c r="E62" s="1">
         <v>0</v>
       </c>
       <c r="P62" s="1">
         <v>0</v>
       </c>
       <c r="T62" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE62" s="1">
         <v>0</v>
       </c>
       <c r="BF62" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO62" s="1">
         <v>0</v>
@@ -5062,13 +5062,13 @@
         <v>5</v>
       </c>
       <c r="BZ62" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI62" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM62" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV62" s="1">
         <v>0</v>
@@ -5078,7 +5078,7 @@
       <c r="A63" s="1">
         <v>0</v>
       </c>
-      <c r="F63" s="1">
+      <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="P63" s="1">
@@ -5109,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="BO63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR63" s="1">
         <v>0</v>
@@ -5134,17 +5134,17 @@
       <c r="A64" s="1">
         <v>0</v>
       </c>
-      <c r="F64" s="1">
-        <v>3</v>
+      <c r="E64" s="1">
+        <v>4</v>
       </c>
       <c r="P64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T64" s="1">
         <v>0</v>
       </c>
       <c r="AE64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI64" s="3">
         <v>0</v>
@@ -5196,14 +5196,14 @@
       <c r="A65" s="1">
         <v>0</v>
       </c>
-      <c r="F65" s="1">
+      <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="P65" s="1">
         <v>0</v>
       </c>
       <c r="T65" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE65" s="1">
         <v>0</v>
@@ -5224,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="BF65" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO65" s="1">
         <v>0</v>
       </c>
       <c r="BZ65" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV65" s="1">
         <v>0</v>
@@ -5240,7 +5240,7 @@
       <c r="A66" s="1">
         <v>0</v>
       </c>
-      <c r="F66" s="1">
+      <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="P66" s="1">
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="BO66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ66" s="1">
         <v>0</v>
@@ -5284,17 +5284,17 @@
       <c r="A67" s="1">
         <v>0</v>
       </c>
-      <c r="F67" s="1">
-        <v>3</v>
+      <c r="E67" s="1">
+        <v>4</v>
       </c>
       <c r="P67" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T67" s="1">
         <v>0</v>
       </c>
       <c r="AE67" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI67" s="3">
         <v>0</v>
@@ -5328,26 +5328,26 @@
       <c r="A68" s="1">
         <v>0</v>
       </c>
-      <c r="F68" s="1">
+      <c r="E68" s="1">
         <v>0</v>
       </c>
       <c r="P68" s="1">
         <v>0</v>
       </c>
       <c r="T68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE68" s="1">
         <v>0</v>
       </c>
       <c r="BF68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO68" s="1">
         <v>0</v>
       </c>
       <c r="BZ68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV68" s="1">
         <v>0</v>
@@ -5357,7 +5357,7 @@
       <c r="A69" s="1">
         <v>0</v>
       </c>
-      <c r="F69" s="1">
+      <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="P69" s="1">
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="BO69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ69" s="1">
         <v>0</v>
@@ -5386,11 +5386,11 @@
       <c r="A70" s="1">
         <v>0</v>
       </c>
-      <c r="F70" s="1">
-        <v>3</v>
+      <c r="E70" s="1">
+        <v>4</v>
       </c>
       <c r="P70" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T70" s="1">
         <v>0</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="AE70" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF70" s="1">
         <v>0</v>
@@ -5424,14 +5424,14 @@
       <c r="A71" s="1">
         <v>0</v>
       </c>
-      <c r="F71" s="1">
+      <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="P71" s="1">
         <v>0</v>
       </c>
       <c r="T71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V71" s="1">
         <v>6</v>
@@ -5455,19 +5455,19 @@
         <v>0</v>
       </c>
       <c r="BF71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO71" s="1">
         <v>0</v>
       </c>
       <c r="BZ71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV71" s="1">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="BO72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ72" s="1">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="AE73" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF73" s="1">
         <v>0</v>
@@ -5626,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z74" s="3">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="BF74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO74" s="1">
         <v>0</v>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="BZ74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA74" s="3">
         <v>0</v>
@@ -5677,10 +5677,10 @@
         <v>0</v>
       </c>
       <c r="CI74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ74" s="3">
         <v>0</v>
@@ -5808,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="BO75" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ75" s="1">
         <v>5</v>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT77" s="4">
         <v>8</v>
@@ -6019,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="BZ77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA77" s="3">
         <v>0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="CI77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ77" s="3">
         <v>0</v>
@@ -6078,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="BO78" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ78" s="1">
         <v>0</v>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT80" s="4">
         <v>8</v>
@@ -6145,13 +6145,13 @@
         <v>0</v>
       </c>
       <c r="BZ80" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI80" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM80" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV80" s="1">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="BO81" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ81" s="1">
         <v>0</v>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT83" s="4">
         <v>8</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="BZ83" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV83" s="1">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="BO84" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ84" s="1">
         <v>0</v>
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="T86" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT86" s="4">
         <v>8</v>
@@ -6331,13 +6331,13 @@
         <v>0</v>
       </c>
       <c r="BZ86" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CI86" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM86" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV86" s="1">
         <v>0</v>
@@ -6613,10 +6613,10 @@
         <v>0</v>
       </c>
       <c r="CI89" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM89" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV89" s="1">
         <v>0</v>
@@ -6715,10 +6715,10 @@
         <v>0</v>
       </c>
       <c r="CI92" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM92" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV92" s="1">
         <v>0</v>
@@ -6772,10 +6772,10 @@
         <v>0</v>
       </c>
       <c r="CI95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV95" s="1">
         <v>0</v>
@@ -6814,10 +6814,10 @@
         <v>0</v>
       </c>
       <c r="CI98" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM98" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS98" s="1">
         <v>0</v>

--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9EE233-C8D8-4502-BF80-198DBB24D6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00DC64D-BBB6-43FB-A3A0-9FAFEFBA0725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2508" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="228" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -729,16 +729,16 @@
       <c r="E2" s="1">
         <v>5</v>
       </c>
-      <c r="AI2" s="4">
+      <c r="AI2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AK2" s="1">
         <v>0</v>
       </c>
       <c r="BK2" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI2" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM2" s="1">
         <v>0</v>
       </c>
       <c r="CR2" s="1">
@@ -749,18 +749,12 @@
       <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="AI3" s="4">
-        <v>8</v>
+      <c r="AI3" s="1">
+        <v>0</v>
       </c>
       <c r="BK3" s="4">
         <v>8</v>
       </c>
-      <c r="CI3" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM3" s="1">
-        <v>4</v>
-      </c>
       <c r="CS3" s="1">
         <v>0</v>
       </c>
@@ -769,16 +763,10 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="AI4" s="4">
-        <v>0</v>
+      <c r="AI4" s="1">
+        <v>4</v>
       </c>
       <c r="BK4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI4" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM4" s="1">
         <v>0</v>
       </c>
       <c r="CT4" s="1">
@@ -789,40 +777,10 @@
       <c r="B5" s="1">
         <v>5</v>
       </c>
-      <c r="AG5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM5" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI5" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM5" s="1">
+      <c r="AI5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="4">
         <v>0</v>
       </c>
       <c r="CU5" s="1">
@@ -833,41 +791,11 @@
       <c r="A6" s="1">
         <v>0</v>
       </c>
-      <c r="AG6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI6" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ6" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK6" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL6" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM6" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI6" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM6" s="1">
-        <v>4</v>
+      <c r="AI6" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK6" s="4">
+        <v>8</v>
       </c>
       <c r="CV6" s="1">
         <v>0</v>
@@ -877,40 +805,10 @@
       <c r="A7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="3">
-        <v>11</v>
-      </c>
-      <c r="AJ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK7" s="3">
-        <v>11</v>
-      </c>
-      <c r="BL7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM7" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI7" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM7" s="1">
+      <c r="AI7" s="4">
+        <v>8</v>
+      </c>
+      <c r="BK7" s="4">
         <v>0</v>
       </c>
       <c r="CV7" s="1">
@@ -921,40 +819,10 @@
       <c r="A8" s="1">
         <v>0</v>
       </c>
-      <c r="AG8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI8" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ8" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK8" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL8" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM8" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI8" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM8" s="1">
+      <c r="AI8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK8" s="1">
         <v>0</v>
       </c>
       <c r="CV8" s="1">
@@ -965,41 +833,17 @@
       <c r="A9" s="1">
         <v>0</v>
       </c>
-      <c r="AG9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI9" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ9" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK9" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL9" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM9" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI9" s="1">
-        <v>4</v>
+      <c r="AI9" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="1">
+        <v>4</v>
+      </c>
+      <c r="CG9" s="1">
+        <v>0</v>
       </c>
       <c r="CM9" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV9" s="1">
         <v>0</v>
@@ -1010,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="AI10" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK10" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI10" s="1">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="BK10" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG10" s="1">
+        <v>4</v>
       </c>
       <c r="CM10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV10" s="1">
         <v>0</v>
@@ -1030,12 +874,18 @@
         <v>0</v>
       </c>
       <c r="AI11" s="4">
-        <v>8</v>
-      </c>
-      <c r="BK11" s="4">
-        <v>8</v>
-      </c>
-      <c r="CI11" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="1">
+        <v>3</v>
+      </c>
+      <c r="BK11" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG11" s="1">
         <v>0</v>
       </c>
       <c r="CM11" s="1">
@@ -1049,17 +899,182 @@
       <c r="A12" s="1">
         <v>0</v>
       </c>
-      <c r="AI12" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK12" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI12" s="1">
-        <v>4</v>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>3</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BJ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BS12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BV12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX12" s="1">
+        <v>3</v>
+      </c>
+      <c r="BY12" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG12" s="1">
+        <v>0</v>
       </c>
       <c r="CM12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV12" s="1">
         <v>0</v>
@@ -1069,188 +1084,38 @@
       <c r="A13" s="1">
         <v>0</v>
       </c>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
       <c r="U13" s="1">
         <v>0</v>
       </c>
-      <c r="V13" s="1">
-        <v>3</v>
-      </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AI13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AL13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AO13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AR13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AU13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="1">
-        <v>3</v>
-      </c>
-      <c r="AX13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BA13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB13" s="1">
-        <v>0</v>
-      </c>
       <c r="BC13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BD13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BG13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BJ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BM13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BP13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BS13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BV13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BY13" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BZ13" s="1">
         <v>0</v>
       </c>
-      <c r="CI13" s="1">
-        <v>0</v>
+      <c r="CA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="CB13" s="1">
+        <v>3</v>
+      </c>
+      <c r="CC13" s="1">
+        <v>0</v>
+      </c>
+      <c r="CD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE13" s="1">
+        <v>3</v>
+      </c>
+      <c r="CF13" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG13" s="1">
+        <v>4</v>
       </c>
       <c r="CM13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV13" s="1">
         <v>0</v>
@@ -1260,14 +1125,35 @@
       <c r="A14" s="1">
         <v>0</v>
       </c>
-      <c r="T14" s="1">
-        <v>4</v>
-      </c>
-      <c r="BC14" s="1">
+      <c r="U14" s="1">
+        <v>4</v>
+      </c>
+      <c r="BB14" s="1">
         <v>0</v>
       </c>
       <c r="BZ14" s="1">
         <v>4</v>
+      </c>
+      <c r="CG14" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM14" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR14" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS14" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT14" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU14" s="3">
+        <v>0</v>
       </c>
       <c r="CV14" s="1">
         <v>0</v>
@@ -1277,13 +1163,34 @@
       <c r="A15" s="1">
         <v>0</v>
       </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB15" s="1">
-        <v>5</v>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="1">
+        <v>0</v>
       </c>
       <c r="BZ15" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG15" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM15" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR15" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS15" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT15" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU15" s="3">
         <v>0</v>
       </c>
       <c r="CV15" s="1">
@@ -1294,13 +1201,43 @@
       <c r="A16" s="1">
         <v>0</v>
       </c>
-      <c r="T16" s="1">
-        <v>0</v>
-      </c>
-      <c r="BA16" s="1">
-        <v>0</v>
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="1">
+        <v>5</v>
       </c>
       <c r="BZ16" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG16" s="1">
+        <v>4</v>
+      </c>
+      <c r="CM16" s="1">
+        <v>4</v>
+      </c>
+      <c r="CN16" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO16" s="4">
+        <v>7</v>
+      </c>
+      <c r="CP16" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ16" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR16" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS16" s="3">
+        <v>11</v>
+      </c>
+      <c r="CT16" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU16" s="3">
         <v>0</v>
       </c>
       <c r="CV16" s="1">
@@ -1311,20 +1248,41 @@
       <c r="A17" s="1">
         <v>0</v>
       </c>
-      <c r="T17" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI17" s="1">
+      <c r="U17" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL17" s="1">
         <v>0</v>
       </c>
       <c r="BZ17" s="1">
         <v>4</v>
+      </c>
+      <c r="CG17" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM17" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ17" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR17" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS17" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT17" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU17" s="3">
+        <v>0</v>
       </c>
       <c r="CV17" s="1">
         <v>0</v>
@@ -1334,55 +1292,40 @@
       <c r="A18" s="1">
         <v>0</v>
       </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="1">
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="1">
         <v>5</v>
       </c>
-      <c r="AY18" s="1">
+      <c r="AX18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK18" s="1">
         <v>5</v>
       </c>
-      <c r="BH18" s="1">
-        <v>5</v>
-      </c>
       <c r="BZ18" s="1">
         <v>0</v>
       </c>
-      <c r="CI18" s="1">
+      <c r="CG18" s="1">
         <v>0</v>
       </c>
       <c r="CM18" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ18" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR18" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS18" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT18" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU18" s="3">
         <v>0</v>
       </c>
       <c r="CV18" s="1">
@@ -1393,52 +1336,22 @@
       <c r="A19" s="1">
         <v>0</v>
       </c>
-      <c r="D19" s="3">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
-        <v>0</v>
-      </c>
-      <c r="O19" s="3">
-        <v>0</v>
-      </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>0</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX19" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG19" s="1">
+      <c r="U19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW19" s="1">
+        <v>5</v>
+      </c>
+      <c r="BJ19" s="1">
         <v>0</v>
       </c>
       <c r="BZ19" s="1">
         <v>0</v>
       </c>
-      <c r="CI19" s="1">
+      <c r="CG19" s="1">
         <v>4</v>
       </c>
       <c r="CM19" s="1">
@@ -1452,52 +1365,79 @@
       <c r="A20" s="1">
         <v>0</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>11</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>11</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <v>7</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>3</v>
       </c>
       <c r="T20" s="1">
-        <v>4</v>
-      </c>
-      <c r="AP20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW20" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="1">
         <v>0</v>
       </c>
       <c r="BZ20" s="1">
         <v>4</v>
       </c>
-      <c r="CI20" s="1">
+      <c r="CG20" s="1">
         <v>0</v>
       </c>
       <c r="CM20" s="1">
@@ -1511,85 +1451,25 @@
       <c r="A21" s="1">
         <v>0</v>
       </c>
-      <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="1">
+      <c r="K21" s="1">
+        <v>4</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="1">
         <v>5</v>
       </c>
-      <c r="AV21" s="1">
+      <c r="BH21" s="1">
         <v>5</v>
       </c>
-      <c r="BE21" s="1">
-        <v>5</v>
-      </c>
       <c r="BZ21" s="1">
         <v>0</v>
       </c>
-      <c r="CA21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI21" s="1">
+      <c r="CG21" s="1">
         <v>0</v>
       </c>
       <c r="CM21" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT21" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU21" s="3">
         <v>0</v>
       </c>
       <c r="CV21" s="1">
@@ -1600,86 +1480,41 @@
       <c r="A22" s="1">
         <v>0</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU22" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD22" s="1">
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG22" s="1">
         <v>0</v>
       </c>
       <c r="BZ22" s="1">
         <v>0</v>
       </c>
-      <c r="CA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI22" s="1">
-        <v>4</v>
+      <c r="CG22" s="1">
+        <v>4</v>
+      </c>
+      <c r="CH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL22" s="3">
+        <v>0</v>
       </c>
       <c r="CM22" s="1">
         <v>4</v>
-      </c>
-      <c r="CQ22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT22" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU22" s="3">
-        <v>0</v>
       </c>
       <c r="CV22" s="1">
         <v>0</v>
@@ -1689,76 +1524,40 @@
       <c r="A23" s="1">
         <v>0</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>4</v>
-      </c>
-      <c r="AM23" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC23" s="1">
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>4</v>
+      </c>
+      <c r="AK23" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF23" s="1">
         <v>0</v>
       </c>
       <c r="BZ23" s="1">
         <v>4</v>
       </c>
-      <c r="CA23" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB23" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC23" s="3">
-        <v>11</v>
-      </c>
-      <c r="CD23" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE23" s="3">
-        <v>0</v>
-      </c>
-      <c r="CF23" s="1">
-        <v>0</v>
-      </c>
       <c r="CG23" s="1">
-        <v>3</v>
-      </c>
-      <c r="CH23" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI23" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL23" s="3">
         <v>0</v>
       </c>
       <c r="CM23" s="1">
-        <v>0</v>
-      </c>
-      <c r="CN23" s="1">
-        <v>0</v>
-      </c>
-      <c r="CO23" s="1">
-        <v>3</v>
-      </c>
-      <c r="CP23" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ23" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR23" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS23" s="3">
-        <v>11</v>
-      </c>
-      <c r="CT23" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU23" s="3">
         <v>0</v>
       </c>
       <c r="CV23" s="1">
@@ -1769,58 +1568,43 @@
       <c r="A24" s="1">
         <v>0</v>
       </c>
-      <c r="H24" s="1">
-        <v>4</v>
-      </c>
-      <c r="M24" s="1">
-        <v>4</v>
-      </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="1">
+      <c r="K24" s="1">
+        <v>4</v>
+      </c>
+      <c r="U24" s="1">
+        <v>0</v>
+      </c>
+      <c r="V24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="1">
         <v>5</v>
       </c>
-      <c r="BB24" s="1">
+      <c r="BE24" s="1">
         <v>5</v>
       </c>
       <c r="BZ24" s="1">
         <v>0</v>
       </c>
-      <c r="CA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI24" s="1">
+      <c r="CG24" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ24" s="3">
+        <v>11</v>
+      </c>
+      <c r="CK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL24" s="3">
         <v>0</v>
       </c>
       <c r="CM24" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT24" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU24" s="3">
         <v>0</v>
       </c>
       <c r="CV24" s="1">
@@ -1831,62 +1615,44 @@
       <c r="A25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="T25" s="1">
+      <c r="K25" s="1">
         <v>0</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
       </c>
-      <c r="AK25" s="1">
-        <v>0</v>
-      </c>
-      <c r="BA25" s="1">
+      <c r="W25" s="1">
+        <v>6</v>
+      </c>
+      <c r="AI25" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD25" s="1">
         <v>0</v>
       </c>
       <c r="BZ25" s="1">
         <v>0</v>
       </c>
-      <c r="CA25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI25" s="1">
-        <v>4</v>
+      <c r="CG25" s="1">
+        <v>4</v>
+      </c>
+      <c r="CH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL25" s="3">
+        <v>0</v>
       </c>
       <c r="CM25" s="1">
         <v>4</v>
-      </c>
-      <c r="CQ25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT25" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU25" s="3">
-        <v>0</v>
       </c>
       <c r="CV25" s="1">
         <v>0</v>
@@ -1896,31 +1662,31 @@
       <c r="A26" s="1">
         <v>0</v>
       </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="T26" s="1">
-        <v>4</v>
-      </c>
-      <c r="V26" s="1">
-        <v>6</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="U26" s="1">
+        <v>4</v>
+      </c>
+      <c r="X26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>7</v>
+      </c>
+      <c r="AA26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="4">
+        <v>7</v>
+      </c>
+      <c r="AD26" s="4">
         <v>0</v>
       </c>
       <c r="AE26" s="1">
@@ -2037,7 +1803,22 @@
       <c r="BZ26" s="1">
         <v>4</v>
       </c>
-      <c r="CI26" s="1">
+      <c r="CG26" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ26" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK26" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL26" s="3">
         <v>0</v>
       </c>
       <c r="CM26" s="1">
@@ -2051,49 +1832,22 @@
       <c r="A27" s="1">
         <v>0</v>
       </c>
-      <c r="H27" s="1">
-        <v>4</v>
-      </c>
-      <c r="M27" s="1">
-        <v>4</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="W27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="K27" s="1">
+        <v>4</v>
+      </c>
+      <c r="U27" s="1">
         <v>0</v>
       </c>
       <c r="AE27" s="1">
         <v>0</v>
       </c>
-      <c r="BJ27" s="4">
+      <c r="BI27" s="4">
         <v>0</v>
       </c>
       <c r="BO27" s="1">
         <v>4</v>
       </c>
       <c r="BZ27" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI27" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM27" s="1">
         <v>0</v>
       </c>
       <c r="CV27" s="1">
@@ -2104,58 +1858,16 @@
       <c r="A28" s="1">
         <v>0</v>
       </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="T28" s="1">
-        <v>0</v>
-      </c>
-      <c r="W28" s="4">
-        <v>0</v>
-      </c>
-      <c r="X28" s="4">
-        <v>7</v>
-      </c>
-      <c r="Y28" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>11</v>
-      </c>
-      <c r="AC28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="3">
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="U28" s="1">
         <v>0</v>
       </c>
       <c r="AE28" s="1">
         <v>4</v>
       </c>
-      <c r="AP28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT28" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ28" s="4">
+      <c r="BI28" s="4">
         <v>8</v>
       </c>
       <c r="BO28" s="1">
@@ -2163,12 +1875,6 @@
       </c>
       <c r="BZ28" s="1">
         <v>0</v>
-      </c>
-      <c r="CI28" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM28" s="1">
-        <v>4</v>
       </c>
       <c r="CV28" s="1">
         <v>0</v>
@@ -2178,55 +1884,16 @@
       <c r="A29" s="1">
         <v>0</v>
       </c>
-      <c r="B29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1">
-        <v>0</v>
-      </c>
-      <c r="T29" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="U29" s="1">
+        <v>4</v>
       </c>
       <c r="AE29" s="1">
         <v>0</v>
       </c>
-      <c r="AP29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT29" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ29" s="4">
+      <c r="BI29" s="4">
         <v>0</v>
       </c>
       <c r="BO29" s="1">
@@ -2234,12 +1901,6 @@
       </c>
       <c r="BZ29" s="1">
         <v>4</v>
-      </c>
-      <c r="CI29" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM29" s="1">
-        <v>0</v>
       </c>
       <c r="CV29" s="1">
         <v>0</v>
@@ -2249,55 +1910,31 @@
       <c r="A30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>4</v>
-      </c>
-      <c r="M30" s="1">
-        <v>4</v>
-      </c>
-      <c r="R30" s="1">
-        <v>5</v>
-      </c>
-      <c r="T30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="3">
+      <c r="K30" s="1">
+        <v>4</v>
+      </c>
+      <c r="U30" s="1">
         <v>0</v>
       </c>
       <c r="AE30" s="1">
         <v>0</v>
       </c>
-      <c r="AP30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="3">
-        <v>11</v>
-      </c>
-      <c r="AS30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ30" s="4">
+      <c r="AV30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="4">
         <v>0</v>
       </c>
       <c r="BO30" s="1">
@@ -2314,40 +1951,31 @@
       <c r="A31" s="1">
         <v>0</v>
       </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
-      <c r="T31" s="1">
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="U31" s="1">
         <v>0</v>
       </c>
       <c r="AE31" s="1">
         <v>4</v>
       </c>
-      <c r="AP31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ31" s="4">
+      <c r="AV31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="4">
         <v>8</v>
       </c>
       <c r="BO31" s="1">
@@ -2364,40 +1992,58 @@
       <c r="A32" s="1">
         <v>0</v>
       </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="T32" s="1">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="1">
         <v>4</v>
       </c>
       <c r="AE32" s="1">
         <v>0</v>
       </c>
-      <c r="AP32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT32" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ32" s="4">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX32" s="3">
+        <v>11</v>
+      </c>
+      <c r="AY32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="4">
         <v>0</v>
       </c>
       <c r="BO32" s="1">
@@ -2414,24 +2060,33 @@
       <c r="A33" s="1">
         <v>0</v>
       </c>
-      <c r="F33" s="1">
-        <v>6</v>
-      </c>
-      <c r="H33" s="1">
-        <v>4</v>
-      </c>
-      <c r="M33" s="1">
-        <v>4</v>
-      </c>
-      <c r="O33" s="1">
-        <v>5</v>
-      </c>
-      <c r="T33" s="1">
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="1">
         <v>0</v>
       </c>
       <c r="AE33" s="1">
         <v>0</v>
       </c>
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
       <c r="AH33" s="3">
         <v>0</v>
       </c>
@@ -2441,40 +2096,37 @@
       <c r="AJ33" s="3">
         <v>0</v>
       </c>
-      <c r="AK33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN33" s="3">
+      <c r="AV33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ33" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI33" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ33" s="1">
+        <v>3</v>
+      </c>
+      <c r="BK33" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL33" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM33" s="1">
+        <v>3</v>
+      </c>
+      <c r="BN33" s="1">
         <v>0</v>
       </c>
       <c r="BO33" s="1">
@@ -2483,7 +2135,7 @@
       <c r="BZ33" s="1">
         <v>0</v>
       </c>
-      <c r="CI33" s="1">
+      <c r="CG33" s="1">
         <v>0</v>
       </c>
       <c r="CM33" s="1">
@@ -2497,26 +2149,35 @@
       <c r="A34" s="1">
         <v>0</v>
       </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="T34" s="1">
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>11</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="1">
         <v>0</v>
       </c>
       <c r="AE34" s="1">
         <v>4</v>
       </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
       <c r="AH34" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI34" s="3">
         <v>0</v>
@@ -2524,40 +2185,19 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
-      <c r="AK34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN34" s="3">
+      <c r="AV34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ34" s="3">
         <v>0</v>
       </c>
       <c r="BO34" s="1">
@@ -2566,7 +2206,7 @@
       <c r="BZ34" s="1">
         <v>0</v>
       </c>
-      <c r="CI34" s="1">
+      <c r="CG34" s="1">
         <v>4</v>
       </c>
       <c r="CM34" s="1">
@@ -2580,12 +2220,33 @@
       <c r="A35" s="1">
         <v>0</v>
       </c>
-      <c r="T35" s="1">
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="1">
         <v>4</v>
       </c>
       <c r="AE35" s="1">
         <v>0</v>
       </c>
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
       <c r="AH35" s="3">
         <v>0</v>
       </c>
@@ -2593,42 +2254,6 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="3">
-        <v>11</v>
-      </c>
-      <c r="AK35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC35" s="3">
-        <v>11</v>
-      </c>
-      <c r="BD35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL35" s="3">
-        <v>11</v>
-      </c>
-      <c r="BM35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN35" s="3">
         <v>0</v>
       </c>
       <c r="BO35" s="1">
@@ -2637,7 +2262,7 @@
       <c r="BZ35" s="1">
         <v>4</v>
       </c>
-      <c r="CI35" s="1">
+      <c r="CG35" s="1">
         <v>0</v>
       </c>
       <c r="CM35" s="1">
@@ -2651,12 +2276,33 @@
       <c r="A36" s="1">
         <v>0</v>
       </c>
-      <c r="T36" s="1">
+      <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+      <c r="U36" s="1">
         <v>0</v>
       </c>
       <c r="AE36" s="1">
         <v>0</v>
       </c>
+      <c r="AF36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="3">
+        <v>0</v>
+      </c>
       <c r="AH36" s="3">
         <v>0</v>
       </c>
@@ -2666,49 +2312,13 @@
       <c r="AJ36" s="3">
         <v>0</v>
       </c>
-      <c r="AK36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN36" s="3">
-        <v>0</v>
-      </c>
       <c r="BO36" s="1">
         <v>4</v>
       </c>
       <c r="BZ36" s="1">
         <v>0</v>
       </c>
-      <c r="CI36" s="1">
+      <c r="CG36" s="1">
         <v>0</v>
       </c>
       <c r="CM36" s="1">
@@ -2722,64 +2332,22 @@
       <c r="A37" s="1">
         <v>0</v>
       </c>
-      <c r="T37" s="1">
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="U37" s="1">
         <v>0</v>
       </c>
       <c r="AE37" s="1">
         <v>4</v>
       </c>
-      <c r="AH37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BB37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN37" s="3">
-        <v>0</v>
-      </c>
       <c r="BO37" s="1">
         <v>0</v>
       </c>
       <c r="BZ37" s="1">
         <v>0</v>
       </c>
-      <c r="CI37" s="1">
+      <c r="CG37" s="1">
         <v>4</v>
       </c>
       <c r="CM37" s="1">
@@ -2793,7 +2361,10 @@
       <c r="A38" s="1">
         <v>0</v>
       </c>
-      <c r="T38" s="1">
+      <c r="K38" s="1">
+        <v>4</v>
+      </c>
+      <c r="U38" s="1">
         <v>4</v>
       </c>
       <c r="AE38" s="1">
@@ -2805,7 +2376,7 @@
       <c r="BZ38" s="1">
         <v>4</v>
       </c>
-      <c r="CI38" s="1">
+      <c r="CG38" s="1">
         <v>0</v>
       </c>
       <c r="CM38" s="1">
@@ -2819,13 +2390,10 @@
       <c r="A39" s="1">
         <v>0</v>
       </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0</v>
-      </c>
-      <c r="T39" s="1">
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="U39" s="1">
         <v>0</v>
       </c>
       <c r="AE39" s="1">
@@ -2837,7 +2405,7 @@
       <c r="BZ39" s="1">
         <v>0</v>
       </c>
-      <c r="CI39" s="1">
+      <c r="CG39" s="1">
         <v>0</v>
       </c>
       <c r="CM39" s="1">
@@ -2851,13 +2419,10 @@
       <c r="A40" s="1">
         <v>0</v>
       </c>
-      <c r="F40" s="1">
-        <v>5</v>
-      </c>
-      <c r="O40" s="1">
-        <v>6</v>
-      </c>
-      <c r="T40" s="1">
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="U40" s="1">
         <v>0</v>
       </c>
       <c r="AE40" s="1">
@@ -2869,7 +2434,7 @@
       <c r="BZ40" s="1">
         <v>0</v>
       </c>
-      <c r="CI40" s="1">
+      <c r="CG40" s="1">
         <v>4</v>
       </c>
       <c r="CM40" s="1">
@@ -2883,13 +2448,10 @@
       <c r="A41" s="1">
         <v>0</v>
       </c>
-      <c r="E41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-      <c r="T41" s="1">
+      <c r="K41" s="1">
+        <v>4</v>
+      </c>
+      <c r="U41" s="1">
         <v>4</v>
       </c>
       <c r="AE41" s="1">
@@ -2961,7 +2523,7 @@
       <c r="BZ41" s="1">
         <v>4</v>
       </c>
-      <c r="CI41" s="1">
+      <c r="CG41" s="1">
         <v>0</v>
       </c>
       <c r="CM41" s="1">
@@ -2975,13 +2537,10 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
-      <c r="D42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>0</v>
-      </c>
-      <c r="T42" s="1">
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1">
         <v>0</v>
       </c>
       <c r="AE42" s="1">
@@ -3053,7 +2612,7 @@
       <c r="BZ42" s="1">
         <v>0</v>
       </c>
-      <c r="CI42" s="1">
+      <c r="CG42" s="1">
         <v>0</v>
       </c>
       <c r="CM42" s="1">
@@ -3067,13 +2626,10 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
-      <c r="C43" s="1">
-        <v>5</v>
-      </c>
-      <c r="R43" s="1">
-        <v>6</v>
-      </c>
-      <c r="T43" s="1">
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="U43" s="1">
         <v>0</v>
       </c>
       <c r="AE43" s="1">
@@ -3145,7 +2701,7 @@
       <c r="BZ43" s="1">
         <v>0</v>
       </c>
-      <c r="CI43" s="1">
+      <c r="CG43" s="1">
         <v>4</v>
       </c>
       <c r="CM43" s="1">
@@ -3159,13 +2715,37 @@
       <c r="A44" s="1">
         <v>0</v>
       </c>
-      <c r="B44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
+      <c r="B44" s="4">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4">
+        <v>7</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4">
+        <v>7</v>
+      </c>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>3</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>4</v>
+      </c>
+      <c r="U44" s="1">
         <v>4</v>
       </c>
       <c r="AE44" s="1">
@@ -3237,7 +2817,7 @@
       <c r="BZ44" s="1">
         <v>4</v>
       </c>
-      <c r="CI44" s="1">
+      <c r="CG44" s="1">
         <v>0</v>
       </c>
       <c r="CM44" s="1">
@@ -3251,7 +2831,10 @@
       <c r="A45" s="1">
         <v>0</v>
       </c>
-      <c r="T45" s="1">
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1">
         <v>0</v>
       </c>
       <c r="AE45" s="1">
@@ -3339,15 +2922,6 @@
         <v>3</v>
       </c>
       <c r="CF45" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG45" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH45" s="1">
-        <v>3</v>
-      </c>
-      <c r="CI45" s="1">
         <v>0</v>
       </c>
       <c r="CM45" s="1">
@@ -3385,7 +2959,28 @@
       <c r="A46" s="1">
         <v>0</v>
       </c>
-      <c r="T46" s="1">
+      <c r="B46" s="1">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>4</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
         <v>0</v>
       </c>
       <c r="AE46" s="1">
@@ -3462,25 +3057,16 @@
       <c r="A47" s="1">
         <v>0</v>
       </c>
-      <c r="T47" s="1">
-        <v>4</v>
+      <c r="K47" s="1">
+        <v>4</v>
+      </c>
+      <c r="U47" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD47" s="1">
+        <v>0</v>
       </c>
       <c r="AE47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="3">
         <v>0</v>
       </c>
       <c r="AN47" s="2">
@@ -3554,40 +3140,16 @@
       <c r="A48" s="1">
         <v>0</v>
       </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="M48" s="1">
-        <v>0</v>
-      </c>
-      <c r="N48" s="1">
-        <v>0</v>
-      </c>
-      <c r="T48" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="1">
-        <v>0</v>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="U48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>5</v>
       </c>
       <c r="AE48" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="3">
         <v>0</v>
       </c>
       <c r="AN48" s="2">
@@ -3661,56 +3223,35 @@
       <c r="A49" s="1">
         <v>0</v>
       </c>
-      <c r="F49" s="1">
-        <v>5</v>
-      </c>
-      <c r="H49" s="1">
-        <v>4</v>
-      </c>
-      <c r="M49" s="1">
-        <v>4</v>
-      </c>
-      <c r="O49" s="1">
-        <v>6</v>
-      </c>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="1">
-        <v>5</v>
+      <c r="K49" s="1">
+        <v>4</v>
+      </c>
+      <c r="U49" s="1">
+        <v>0</v>
+      </c>
+      <c r="V49" s="4">
+        <v>0</v>
+      </c>
+      <c r="W49" s="4">
+        <v>7</v>
+      </c>
+      <c r="X49" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="4">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="1">
+        <v>0</v>
       </c>
       <c r="AE49" s="1">
         <v>4</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>11</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>0</v>
       </c>
       <c r="AN49" s="2">
         <v>0</v>
@@ -3783,55 +3324,13 @@
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="E50" s="1">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="1">
-        <v>4</v>
-      </c>
-      <c r="U50" s="3">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3">
-        <v>0</v>
-      </c>
-      <c r="W50" s="3">
-        <v>0</v>
-      </c>
-      <c r="X50" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="1">
-        <v>0</v>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
+        <v>4</v>
       </c>
       <c r="AE50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ50" s="3">
         <v>0</v>
       </c>
       <c r="AN50" s="2">
@@ -3905,61 +3404,25 @@
       <c r="A51" s="1">
         <v>0</v>
       </c>
-      <c r="E51" s="4">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="M51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="4">
-        <v>0</v>
-      </c>
-      <c r="T51" s="1">
-        <v>0</v>
-      </c>
-      <c r="U51" s="3">
-        <v>0</v>
-      </c>
-      <c r="V51" s="3">
-        <v>0</v>
-      </c>
-      <c r="W51" s="3">
-        <v>11</v>
-      </c>
-      <c r="X51" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="4">
-        <v>7</v>
-      </c>
-      <c r="AB51" s="4">
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="1">
         <v>0</v>
       </c>
       <c r="AE51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="3">
         <v>0</v>
       </c>
       <c r="AN51" s="2">
@@ -4033,34 +3496,22 @@
       <c r="A52" s="1">
         <v>0</v>
       </c>
-      <c r="E52" s="4">
-        <v>8</v>
-      </c>
-      <c r="H52" s="1">
-        <v>4</v>
-      </c>
-      <c r="M52" s="1">
-        <v>4</v>
-      </c>
-      <c r="P52" s="4">
-        <v>8</v>
-      </c>
-      <c r="T52" s="1">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
         <v>0</v>
       </c>
       <c r="AE52" s="1">
@@ -4137,35 +3588,23 @@
       <c r="A53" s="1">
         <v>0</v>
       </c>
-      <c r="E53" s="4">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="M53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="4">
-        <v>0</v>
-      </c>
-      <c r="T53" s="1">
-        <v>4</v>
-      </c>
-      <c r="U53" s="3">
-        <v>0</v>
-      </c>
-      <c r="V53" s="3">
-        <v>0</v>
-      </c>
-      <c r="W53" s="3">
-        <v>0</v>
-      </c>
-      <c r="X53" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="3">
-        <v>0</v>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3">
+        <v>11</v>
+      </c>
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="1">
+        <v>4</v>
       </c>
       <c r="AE53" s="1">
         <v>0</v>
@@ -4241,19 +3680,22 @@
       <c r="A54" s="1">
         <v>0</v>
       </c>
-      <c r="E54" s="4">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="M54" s="1">
-        <v>0</v>
-      </c>
-      <c r="P54" s="4">
-        <v>0</v>
-      </c>
-      <c r="T54" s="1">
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+      <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1">
         <v>0</v>
       </c>
       <c r="AE54" s="1">
@@ -4330,19 +3772,22 @@
       <c r="A55" s="1">
         <v>0</v>
       </c>
-      <c r="E55" s="4">
-        <v>8</v>
-      </c>
-      <c r="H55" s="1">
-        <v>4</v>
-      </c>
-      <c r="M55" s="1">
-        <v>4</v>
-      </c>
-      <c r="P55" s="4">
-        <v>8</v>
-      </c>
-      <c r="T55" s="1">
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+      <c r="L55" s="3">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1">
         <v>0</v>
       </c>
       <c r="AE55" s="1">
@@ -4450,15 +3895,6 @@
       <c r="CF55" s="1">
         <v>0</v>
       </c>
-      <c r="CG55" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH55" s="1">
-        <v>3</v>
-      </c>
-      <c r="CI55" s="1">
-        <v>0</v>
-      </c>
       <c r="CM55" s="1">
         <v>0</v>
       </c>
@@ -4494,19 +3930,10 @@
       <c r="A56" s="1">
         <v>0</v>
       </c>
-      <c r="E56" s="4">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="4">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="1">
         <v>4</v>
       </c>
       <c r="AE56" s="1">
@@ -4584,11 +4011,11 @@
       <c r="BZ56" s="1">
         <v>4</v>
       </c>
-      <c r="CI56" s="1">
-        <v>4</v>
+      <c r="CG56" s="1">
+        <v>0</v>
       </c>
       <c r="CM56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV56" s="1">
         <v>0</v>
@@ -4598,19 +4025,10 @@
       <c r="A57" s="1">
         <v>0</v>
       </c>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
+      <c r="K57" s="1">
+        <v>4</v>
+      </c>
+      <c r="U57" s="1">
         <v>0</v>
       </c>
       <c r="AE57" s="1">
@@ -4688,11 +4106,11 @@
       <c r="BZ57" s="1">
         <v>0</v>
       </c>
-      <c r="CI57" s="1">
-        <v>0</v>
+      <c r="CG57" s="1">
+        <v>4</v>
       </c>
       <c r="CM57" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV57" s="1">
         <v>0</v>
@@ -4702,19 +4120,10 @@
       <c r="A58" s="1">
         <v>0</v>
       </c>
-      <c r="F58" s="1">
-        <v>6</v>
-      </c>
-      <c r="H58" s="1">
-        <v>4</v>
-      </c>
-      <c r="M58" s="1">
-        <v>4</v>
-      </c>
-      <c r="O58" s="1">
-        <v>5</v>
-      </c>
-      <c r="T58" s="1">
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="1">
         <v>0</v>
       </c>
       <c r="AE58" s="1">
@@ -4792,7 +4201,7 @@
       <c r="BZ58" s="1">
         <v>0</v>
       </c>
-      <c r="CI58" s="1">
+      <c r="CG58" s="1">
         <v>0</v>
       </c>
       <c r="CM58" s="1">
@@ -4806,19 +4215,10 @@
       <c r="A59" s="1">
         <v>0</v>
       </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1">
+      <c r="K59" s="4">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1">
         <v>4</v>
       </c>
       <c r="AE59" s="1">
@@ -4890,11 +4290,11 @@
       <c r="BZ59" s="1">
         <v>4</v>
       </c>
-      <c r="CI59" s="1">
-        <v>4</v>
+      <c r="CG59" s="1">
+        <v>0</v>
       </c>
       <c r="CM59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV59" s="1">
         <v>0</v>
@@ -4904,13 +4304,10 @@
       <c r="A60" s="1">
         <v>0</v>
       </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="1">
+      <c r="K60" s="4">
+        <v>8</v>
+      </c>
+      <c r="U60" s="1">
         <v>0</v>
       </c>
       <c r="AE60" s="1">
@@ -4982,11 +4379,11 @@
       <c r="BZ60" s="1">
         <v>0</v>
       </c>
-      <c r="CI60" s="1">
-        <v>0</v>
+      <c r="CG60" s="1">
+        <v>4</v>
       </c>
       <c r="CM60" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV60" s="1">
         <v>0</v>
@@ -4996,13 +4393,10 @@
       <c r="A61" s="1">
         <v>0</v>
       </c>
-      <c r="F61" s="1">
-        <v>5</v>
-      </c>
-      <c r="O61" s="1">
-        <v>6</v>
-      </c>
-      <c r="T61" s="1">
+      <c r="K61" s="4">
+        <v>0</v>
+      </c>
+      <c r="U61" s="1">
         <v>0</v>
       </c>
       <c r="AE61" s="1">
@@ -5023,7 +4417,7 @@
       <c r="BZ61" s="1">
         <v>0</v>
       </c>
-      <c r="CI61" s="1">
+      <c r="CG61" s="1">
         <v>0</v>
       </c>
       <c r="CM61" s="1">
@@ -5037,13 +4431,10 @@
       <c r="A62" s="1">
         <v>0</v>
       </c>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
-      <c r="P62" s="1">
-        <v>0</v>
-      </c>
-      <c r="T62" s="1">
+      <c r="K62" s="4">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1">
         <v>4</v>
       </c>
       <c r="AE62" s="1">
@@ -5064,11 +4455,11 @@
       <c r="BZ62" s="1">
         <v>4</v>
       </c>
-      <c r="CI62" s="1">
-        <v>4</v>
+      <c r="CG62" s="1">
+        <v>0</v>
       </c>
       <c r="CM62" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV62" s="1">
         <v>0</v>
@@ -5078,33 +4469,15 @@
       <c r="A63" s="1">
         <v>0</v>
       </c>
-      <c r="E63" s="1">
-        <v>0</v>
-      </c>
-      <c r="P63" s="1">
-        <v>0</v>
-      </c>
-      <c r="T63" s="1">
+      <c r="K63" s="4">
+        <v>8</v>
+      </c>
+      <c r="U63" s="1">
         <v>0</v>
       </c>
       <c r="AE63" s="1">
         <v>0</v>
       </c>
-      <c r="AI63" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ63" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK63" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL63" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM63" s="3">
-        <v>0</v>
-      </c>
       <c r="BF63" s="1">
         <v>0</v>
       </c>
@@ -5120,11 +4493,11 @@
       <c r="BZ63" s="1">
         <v>0</v>
       </c>
-      <c r="CI63" s="1">
-        <v>0</v>
+      <c r="CG63" s="1">
+        <v>4</v>
       </c>
       <c r="CM63" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV63" s="1">
         <v>0</v>
@@ -5134,32 +4507,14 @@
       <c r="A64" s="1">
         <v>0</v>
       </c>
-      <c r="E64" s="1">
-        <v>4</v>
-      </c>
-      <c r="P64" s="1">
-        <v>4</v>
-      </c>
-      <c r="T64" s="1">
+      <c r="K64" s="4">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
         <v>0</v>
       </c>
       <c r="AE64" s="1">
         <v>4</v>
-      </c>
-      <c r="AI64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM64" s="3">
-        <v>0</v>
       </c>
       <c r="BF64" s="1">
         <v>0</v>
@@ -5188,6 +4543,12 @@
       <c r="BZ64" s="1">
         <v>0</v>
       </c>
+      <c r="CG64" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM64" s="1">
+        <v>0</v>
+      </c>
       <c r="CV64" s="1">
         <v>0</v>
       </c>
@@ -5196,31 +4557,13 @@
       <c r="A65" s="1">
         <v>0</v>
       </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1">
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
         <v>4</v>
       </c>
       <c r="AE65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI65" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ65" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK65" s="3">
-        <v>11</v>
-      </c>
-      <c r="AL65" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM65" s="3">
         <v>0</v>
       </c>
       <c r="BF65" s="1">
@@ -5240,31 +4583,13 @@
       <c r="A66" s="1">
         <v>0</v>
       </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="1">
+      <c r="K66" s="1">
+        <v>4</v>
+      </c>
+      <c r="U66" s="1">
         <v>0</v>
       </c>
       <c r="AE66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM66" s="3">
         <v>0</v>
       </c>
       <c r="BF66" s="1">
@@ -5284,32 +4609,14 @@
       <c r="A67" s="1">
         <v>0</v>
       </c>
-      <c r="E67" s="1">
-        <v>4</v>
-      </c>
-      <c r="P67" s="1">
-        <v>4</v>
-      </c>
-      <c r="T67" s="1">
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1">
         <v>0</v>
       </c>
       <c r="AE67" s="1">
         <v>4</v>
-      </c>
-      <c r="AI67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM67" s="3">
-        <v>0</v>
       </c>
       <c r="BF67" s="1">
         <v>0</v>
@@ -5328,13 +4635,10 @@
       <c r="A68" s="1">
         <v>0</v>
       </c>
-      <c r="E68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="1">
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
         <v>4</v>
       </c>
       <c r="AE68" s="1">
@@ -5357,13 +4661,10 @@
       <c r="A69" s="1">
         <v>0</v>
       </c>
-      <c r="E69" s="1">
-        <v>0</v>
-      </c>
-      <c r="P69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="1">
+      <c r="K69" s="1">
+        <v>4</v>
+      </c>
+      <c r="U69" s="1">
         <v>0</v>
       </c>
       <c r="AE69" s="1">
@@ -5386,13 +4687,7 @@
       <c r="A70" s="1">
         <v>0</v>
       </c>
-      <c r="E70" s="1">
-        <v>4</v>
-      </c>
-      <c r="P70" s="1">
-        <v>4</v>
-      </c>
-      <c r="T70" s="1">
+      <c r="K70" s="1">
         <v>0</v>
       </c>
       <c r="U70" s="1">
@@ -5401,6 +4696,21 @@
       <c r="AE70" s="1">
         <v>4</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
       <c r="BF70" s="1">
         <v>0</v>
       </c>
@@ -5410,7 +4720,7 @@
       <c r="BZ70" s="1">
         <v>0</v>
       </c>
-      <c r="CI70" s="1">
+      <c r="CG70" s="1">
         <v>0</v>
       </c>
       <c r="CM70" s="1">
@@ -5424,36 +4734,30 @@
       <c r="A71" s="1">
         <v>0</v>
       </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="P71" s="1">
-        <v>0</v>
-      </c>
-      <c r="T71" s="1">
-        <v>4</v>
-      </c>
-      <c r="V71" s="1">
-        <v>6</v>
-      </c>
-      <c r="Z71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD71" s="3">
-        <v>0</v>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="U71" s="1">
+        <v>4</v>
       </c>
       <c r="AE71" s="1">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
       <c r="BF71" s="1">
         <v>4</v>
       </c>
@@ -5463,7 +4767,7 @@
       <c r="BZ71" s="1">
         <v>4</v>
       </c>
-      <c r="CI71" s="1">
+      <c r="CG71" s="1">
         <v>4</v>
       </c>
       <c r="CM71" s="1">
@@ -5477,30 +4781,30 @@
       <c r="A72" s="1">
         <v>0</v>
       </c>
-      <c r="T72" s="1">
-        <v>0</v>
-      </c>
-      <c r="W72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="K72" s="1">
+        <v>4</v>
+      </c>
+      <c r="U72" s="1">
         <v>0</v>
       </c>
       <c r="AE72" s="1">
         <v>0</v>
       </c>
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="3">
+        <v>11</v>
+      </c>
+      <c r="AL72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="3">
+        <v>0</v>
+      </c>
       <c r="BF72" s="1">
         <v>0</v>
       </c>
@@ -5510,7 +4814,7 @@
       <c r="BZ72" s="1">
         <v>0</v>
       </c>
-      <c r="CI72" s="1">
+      <c r="CG72" s="1">
         <v>0</v>
       </c>
       <c r="CM72" s="1">
@@ -5524,35 +4828,32 @@
       <c r="A73" s="1">
         <v>0</v>
       </c>
-      <c r="T73" s="1">
-        <v>0</v>
-      </c>
-      <c r="W73" s="4">
-        <v>0</v>
-      </c>
-      <c r="X73" s="4">
-        <v>7</v>
-      </c>
-      <c r="Y73" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="3">
-        <v>11</v>
-      </c>
-      <c r="AC73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD73" s="3">
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="U73" s="1">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1">
         <v>0</v>
       </c>
       <c r="AE73" s="1">
         <v>4</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
       </c>
       <c r="BF73" s="1">
         <v>0</v>
@@ -5581,40 +4882,10 @@
       <c r="BZ73" s="1">
         <v>0</v>
       </c>
-      <c r="CA73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI73" s="1">
+      <c r="CG73" s="1">
         <v>0</v>
       </c>
       <c r="CM73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT73" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU73" s="3">
         <v>0</v>
       </c>
       <c r="CV73" s="1">
@@ -5625,27 +4896,33 @@
       <c r="A74" s="1">
         <v>0</v>
       </c>
-      <c r="T74" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD74" s="3">
-        <v>0</v>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="U74" s="1">
+        <v>4</v>
+      </c>
+      <c r="W74" s="1">
+        <v>6</v>
       </c>
       <c r="AE74" s="1">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
       <c r="BF74" s="1">
         <v>4</v>
       </c>
@@ -5661,41 +4938,11 @@
       <c r="BZ74" s="1">
         <v>4</v>
       </c>
-      <c r="CA74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI74" s="1">
+      <c r="CG74" s="1">
         <v>4</v>
       </c>
       <c r="CM74" s="1">
         <v>4</v>
-      </c>
-      <c r="CQ74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT74" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU74" s="3">
-        <v>0</v>
       </c>
       <c r="CV74" s="1">
         <v>0</v>
@@ -5705,22 +4952,58 @@
       <c r="A75" s="1">
         <v>0</v>
       </c>
+      <c r="K75" s="1">
+        <v>4</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>3</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0</v>
+      </c>
+      <c r="O75" s="1">
+        <v>0</v>
+      </c>
+      <c r="P75" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>0</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="S75" s="1">
+        <v>3</v>
+      </c>
       <c r="T75" s="1">
         <v>0</v>
       </c>
-      <c r="Z75" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC75" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD75" s="3">
+      <c r="U75" s="1">
+        <v>0</v>
+      </c>
+      <c r="X75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="4">
+        <v>7</v>
+      </c>
+      <c r="AA75" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="4">
+        <v>7</v>
+      </c>
+      <c r="AD75" s="4">
         <v>0</v>
       </c>
       <c r="AE75" s="1">
@@ -5819,58 +5102,10 @@
       <c r="BZ75" s="1">
         <v>0</v>
       </c>
-      <c r="CA75" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB75" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC75" s="3">
-        <v>11</v>
-      </c>
-      <c r="CD75" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE75" s="3">
-        <v>0</v>
-      </c>
-      <c r="CF75" s="1">
-        <v>0</v>
-      </c>
       <c r="CG75" s="1">
-        <v>3</v>
-      </c>
-      <c r="CH75" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI75" s="1">
         <v>0</v>
       </c>
       <c r="CM75" s="1">
-        <v>0</v>
-      </c>
-      <c r="CN75" s="1">
-        <v>0</v>
-      </c>
-      <c r="CO75" s="1">
-        <v>3</v>
-      </c>
-      <c r="CP75" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ75" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR75" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS75" s="3">
-        <v>11</v>
-      </c>
-      <c r="CT75" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU75" s="3">
         <v>0</v>
       </c>
       <c r="CV75" s="1">
@@ -5881,7 +5116,10 @@
       <c r="A76" s="1">
         <v>0</v>
       </c>
-      <c r="T76" s="1">
+      <c r="U76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1">
         <v>0</v>
       </c>
       <c r="AT76" s="4">
@@ -5905,40 +5143,10 @@
       <c r="BZ76" s="1">
         <v>0</v>
       </c>
-      <c r="CA76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI76" s="1">
+      <c r="CG76" s="1">
         <v>0</v>
       </c>
       <c r="CM76" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT76" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU76" s="3">
         <v>0</v>
       </c>
       <c r="CV76" s="1">
@@ -5949,61 +5157,10 @@
       <c r="A77" s="1">
         <v>0</v>
       </c>
-      <c r="B77" s="1">
-        <v>0</v>
-      </c>
-      <c r="C77" s="1">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1">
-        <v>0</v>
-      </c>
-      <c r="E77" s="1">
-        <v>0</v>
-      </c>
-      <c r="F77" s="1">
-        <v>3</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
-      </c>
-      <c r="H77" s="4">
-        <v>0</v>
-      </c>
-      <c r="I77" s="4">
-        <v>7</v>
-      </c>
-      <c r="J77" s="4">
-        <v>0</v>
-      </c>
-      <c r="K77" s="4">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4">
-        <v>7</v>
-      </c>
-      <c r="M77" s="4">
-        <v>0</v>
-      </c>
-      <c r="N77" s="1">
-        <v>0</v>
-      </c>
-      <c r="O77" s="1">
-        <v>3</v>
-      </c>
-      <c r="P77" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="1">
-        <v>0</v>
-      </c>
-      <c r="R77" s="1">
-        <v>3</v>
-      </c>
-      <c r="S77" s="1">
-        <v>0</v>
-      </c>
-      <c r="T77" s="1">
+      <c r="U77" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE77" s="1">
         <v>4</v>
       </c>
       <c r="AT77" s="4">
@@ -6021,41 +5178,11 @@
       <c r="BZ77" s="1">
         <v>4</v>
       </c>
-      <c r="CA77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI77" s="1">
+      <c r="CG77" s="1">
         <v>4</v>
       </c>
       <c r="CM77" s="1">
         <v>4</v>
-      </c>
-      <c r="CQ77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT77" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU77" s="3">
-        <v>0</v>
       </c>
       <c r="CV77" s="1">
         <v>0</v>
@@ -6065,7 +5192,10 @@
       <c r="A78" s="1">
         <v>0</v>
       </c>
-      <c r="T78" s="1">
+      <c r="U78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
         <v>0</v>
       </c>
       <c r="AT78" s="4">
@@ -6083,7 +5213,7 @@
       <c r="BZ78" s="1">
         <v>0</v>
       </c>
-      <c r="CI78" s="1">
+      <c r="CG78" s="1">
         <v>0</v>
       </c>
       <c r="CM78" s="1">
@@ -6097,7 +5227,10 @@
       <c r="A79" s="1">
         <v>0</v>
       </c>
-      <c r="T79" s="1">
+      <c r="U79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1">
         <v>0</v>
       </c>
       <c r="AT79" s="4">
@@ -6115,7 +5248,7 @@
       <c r="BZ79" s="1">
         <v>0</v>
       </c>
-      <c r="CI79" s="1">
+      <c r="CG79" s="1">
         <v>0</v>
       </c>
       <c r="CM79" s="1">
@@ -6129,7 +5262,10 @@
       <c r="A80" s="1">
         <v>0</v>
       </c>
-      <c r="T80" s="1">
+      <c r="U80" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE80" s="1">
         <v>4</v>
       </c>
       <c r="AT80" s="4">
@@ -6147,7 +5283,7 @@
       <c r="BZ80" s="1">
         <v>4</v>
       </c>
-      <c r="CI80" s="1">
+      <c r="CG80" s="1">
         <v>4</v>
       </c>
       <c r="CM80" s="1">
@@ -6161,7 +5297,10 @@
       <c r="A81" s="1">
         <v>0</v>
       </c>
-      <c r="T81" s="1">
+      <c r="U81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="1">
         <v>0</v>
       </c>
       <c r="AT81" s="4">
@@ -6179,7 +5318,7 @@
       <c r="BZ81" s="1">
         <v>0</v>
       </c>
-      <c r="CI81" s="1">
+      <c r="CG81" s="1">
         <v>0</v>
       </c>
       <c r="CM81" s="1">
@@ -6193,7 +5332,10 @@
       <c r="A82" s="1">
         <v>0</v>
       </c>
-      <c r="T82" s="1">
+      <c r="U82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL82" s="1">
         <v>0</v>
       </c>
       <c r="AT82" s="4">
@@ -6209,6 +5351,12 @@
         <v>0</v>
       </c>
       <c r="BZ82" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG82" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM82" s="1">
         <v>0</v>
       </c>
       <c r="CV82" s="1">
@@ -6219,7 +5367,10 @@
       <c r="A83" s="1">
         <v>0</v>
       </c>
-      <c r="T83" s="1">
+      <c r="U83" s="1">
+        <v>4</v>
+      </c>
+      <c r="AL83" s="1">
         <v>4</v>
       </c>
       <c r="AT83" s="4">
@@ -6237,6 +5388,12 @@
       <c r="BZ83" s="1">
         <v>4</v>
       </c>
+      <c r="CG83" s="1">
+        <v>4</v>
+      </c>
+      <c r="CM83" s="1">
+        <v>4</v>
+      </c>
       <c r="CV83" s="1">
         <v>0</v>
       </c>
@@ -6245,7 +5402,10 @@
       <c r="A84" s="1">
         <v>0</v>
       </c>
-      <c r="T84" s="1">
+      <c r="U84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="1">
         <v>0</v>
       </c>
       <c r="AT84" s="4">
@@ -6261,6 +5421,12 @@
         <v>4</v>
       </c>
       <c r="BZ84" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG84" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM84" s="1">
         <v>0</v>
       </c>
       <c r="CV84" s="1">
@@ -6271,7 +5437,10 @@
       <c r="A85" s="1">
         <v>0</v>
       </c>
-      <c r="T85" s="1">
+      <c r="U85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="1">
         <v>0</v>
       </c>
       <c r="AT85" s="4">
@@ -6289,7 +5458,7 @@
       <c r="BZ85" s="1">
         <v>0</v>
       </c>
-      <c r="CI85" s="1">
+      <c r="CG85" s="1">
         <v>0</v>
       </c>
       <c r="CM85" s="1">
@@ -6303,7 +5472,10 @@
       <c r="A86" s="1">
         <v>0</v>
       </c>
-      <c r="T86" s="1">
+      <c r="U86" s="1">
+        <v>4</v>
+      </c>
+      <c r="AL86" s="1">
         <v>4</v>
       </c>
       <c r="AT86" s="4">
@@ -6333,7 +5505,7 @@
       <c r="BZ86" s="1">
         <v>4</v>
       </c>
-      <c r="CI86" s="1">
+      <c r="CG86" s="1">
         <v>4</v>
       </c>
       <c r="CM86" s="1">
@@ -6347,7 +5519,10 @@
       <c r="A87" s="1">
         <v>0</v>
       </c>
-      <c r="T87" s="1">
+      <c r="U87" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="1">
         <v>0</v>
       </c>
       <c r="AT87" s="4">
@@ -6377,10 +5552,25 @@
       <c r="BZ87" s="1">
         <v>0</v>
       </c>
-      <c r="CI87" s="1">
+      <c r="CG87" s="1">
         <v>0</v>
       </c>
       <c r="CM87" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR87" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS87" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT87" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU87" s="3">
         <v>0</v>
       </c>
       <c r="CV87" s="1">
@@ -6391,6 +5581,60 @@
       <c r="A88" s="1">
         <v>0</v>
       </c>
+      <c r="B88" s="1">
+        <v>0</v>
+      </c>
+      <c r="C88" s="1">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1">
+        <v>0</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1">
+        <v>3</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="4">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4">
+        <v>7</v>
+      </c>
+      <c r="J88" s="4">
+        <v>0</v>
+      </c>
+      <c r="K88" s="4">
+        <v>0</v>
+      </c>
+      <c r="L88" s="4">
+        <v>7</v>
+      </c>
+      <c r="M88" s="4">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1">
+        <v>0</v>
+      </c>
+      <c r="O88" s="1">
+        <v>3</v>
+      </c>
+      <c r="P88" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="1">
+        <v>0</v>
+      </c>
+      <c r="R88" s="1">
+        <v>3</v>
+      </c>
+      <c r="S88" s="1">
+        <v>0</v>
+      </c>
       <c r="T88" s="1">
         <v>0</v>
       </c>
@@ -6568,10 +5812,43 @@
       <c r="BZ88" s="1">
         <v>0</v>
       </c>
-      <c r="CI88" s="1">
+      <c r="CA88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CB88" s="4">
+        <v>7</v>
+      </c>
+      <c r="CC88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE88" s="4">
+        <v>7</v>
+      </c>
+      <c r="CF88" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG88" s="1">
         <v>0</v>
       </c>
       <c r="CM88" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR88" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS88" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT88" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU88" s="3">
         <v>0</v>
       </c>
       <c r="CV88" s="1">
@@ -6582,19 +5859,7 @@
       <c r="A89" s="1">
         <v>0</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="AX89" s="1">
         <v>0</v>
       </c>
       <c r="BM89" s="3">
@@ -6612,11 +5877,35 @@
       <c r="BQ89" s="3">
         <v>0</v>
       </c>
-      <c r="CI89" s="1">
+      <c r="CG89" s="1">
         <v>4</v>
       </c>
       <c r="CM89" s="1">
         <v>4</v>
+      </c>
+      <c r="CN89" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO89" s="4">
+        <v>7</v>
+      </c>
+      <c r="CP89" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ89" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR89" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS89" s="3">
+        <v>11</v>
+      </c>
+      <c r="CT89" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU89" s="3">
+        <v>0</v>
       </c>
       <c r="CV89" s="1">
         <v>0</v>
@@ -6626,20 +5915,8 @@
       <c r="A90" s="1">
         <v>0</v>
       </c>
-      <c r="I90" s="3">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3">
-        <v>0</v>
-      </c>
-      <c r="L90" s="3">
-        <v>0</v>
-      </c>
-      <c r="M90" s="3">
-        <v>0</v>
+      <c r="AX90" s="1">
+        <v>4</v>
       </c>
       <c r="BM90" s="3">
         <v>0</v>
@@ -6656,10 +5933,25 @@
       <c r="BQ90" s="3">
         <v>0</v>
       </c>
-      <c r="CI90" s="1">
+      <c r="CG90" s="1">
         <v>0</v>
       </c>
       <c r="CM90" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ90" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR90" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS90" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT90" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU90" s="3">
         <v>0</v>
       </c>
       <c r="CV90" s="1">
@@ -6670,25 +5962,28 @@
       <c r="A91" s="1">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>11</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI91" s="1">
+      <c r="AX91" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG91" s="1">
         <v>0</v>
       </c>
       <c r="CM91" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR91" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS91" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT91" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU91" s="3">
         <v>0</v>
       </c>
       <c r="CV91" s="1">
@@ -6699,22 +5994,22 @@
       <c r="A92" s="1">
         <v>0</v>
       </c>
-      <c r="I92" s="3">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3">
-        <v>0</v>
-      </c>
-      <c r="K92" s="3">
-        <v>0</v>
-      </c>
-      <c r="L92" s="3">
-        <v>0</v>
-      </c>
-      <c r="M92" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI92" s="1">
+      <c r="AV92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG92" s="1">
         <v>4</v>
       </c>
       <c r="CM92" s="1">
@@ -6728,22 +6023,22 @@
       <c r="A93" s="1">
         <v>0</v>
       </c>
-      <c r="I93" s="3">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3">
-        <v>0</v>
-      </c>
-      <c r="L93" s="3">
-        <v>0</v>
-      </c>
-      <c r="M93" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI93" s="1">
+      <c r="AV93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG93" s="1">
         <v>0</v>
       </c>
       <c r="CM93" s="1">
@@ -6757,10 +6052,19 @@
       <c r="A94" s="1">
         <v>0</v>
       </c>
-      <c r="CI94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM94" s="1">
+      <c r="AV94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX94" s="3">
+        <v>11</v>
+      </c>
+      <c r="AY94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ94" s="3">
         <v>0</v>
       </c>
       <c r="CV94" s="1">
@@ -6771,11 +6075,20 @@
       <c r="A95" s="1">
         <v>0</v>
       </c>
-      <c r="CI95" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM95" s="1">
-        <v>4</v>
+      <c r="AV95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ95" s="3">
+        <v>0</v>
       </c>
       <c r="CV95" s="1">
         <v>0</v>
@@ -6785,10 +6098,19 @@
       <c r="B96" s="1">
         <v>6</v>
       </c>
-      <c r="CI96" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM96" s="1">
+      <c r="AV96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ96" s="3">
         <v>0</v>
       </c>
       <c r="CU96" s="1">
@@ -6799,10 +6121,7 @@
       <c r="C97" s="1">
         <v>0</v>
       </c>
-      <c r="CI97" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM97" s="1">
+      <c r="AX97" s="1">
         <v>0</v>
       </c>
       <c r="CT97" s="1">
@@ -6813,10 +6132,7 @@
       <c r="D98" s="1">
         <v>0</v>
       </c>
-      <c r="CI98" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM98" s="1">
+      <c r="AX98" s="1">
         <v>4</v>
       </c>
       <c r="CS98" s="1">
@@ -6827,10 +6143,7 @@
       <c r="E99" s="1">
         <v>6</v>
       </c>
-      <c r="CI99" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM99" s="1">
+      <c r="AX99" s="1">
         <v>0</v>
       </c>
       <c r="CR99" s="1">

--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00DC64D-BBB6-43FB-A3A0-9FAFEFBA0725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E217DC-E84D-4FD0-B53B-8B4AA06510C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="228" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="2304" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1087,7 +1087,7 @@
       <c r="U13" s="1">
         <v>0</v>
       </c>
-      <c r="BC13" s="1">
+      <c r="BB13" s="1">
         <v>5</v>
       </c>
       <c r="BZ13" s="1">
@@ -1128,7 +1128,7 @@
       <c r="U14" s="1">
         <v>4</v>
       </c>
-      <c r="BB14" s="1">
+      <c r="BA14" s="1">
         <v>0</v>
       </c>
       <c r="BZ14" s="1">
@@ -1166,7 +1166,7 @@
       <c r="U15" s="1">
         <v>0</v>
       </c>
-      <c r="BA15" s="1">
+      <c r="AZ15" s="1">
         <v>0</v>
       </c>
       <c r="BZ15" s="1">
@@ -1204,7 +1204,7 @@
       <c r="U16" s="1">
         <v>0</v>
       </c>
-      <c r="AZ16" s="1">
+      <c r="AY16" s="1">
         <v>5</v>
       </c>
       <c r="BZ16" s="1">
@@ -1251,13 +1251,7 @@
       <c r="U17" s="1">
         <v>4</v>
       </c>
-      <c r="AQ17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY17" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL17" s="1">
+      <c r="AX17" s="1">
         <v>0</v>
       </c>
       <c r="BZ17" s="1">
@@ -1295,14 +1289,8 @@
       <c r="U18" s="1">
         <v>0</v>
       </c>
-      <c r="AP18" s="1">
-        <v>5</v>
-      </c>
-      <c r="AX18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK18" s="1">
-        <v>5</v>
+      <c r="AW18" s="1">
+        <v>0</v>
       </c>
       <c r="BZ18" s="1">
         <v>0</v>
@@ -1339,14 +1327,8 @@
       <c r="U19" s="1">
         <v>0</v>
       </c>
-      <c r="AO19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW19" s="1">
+      <c r="AV19" s="1">
         <v>5</v>
-      </c>
-      <c r="BJ19" s="1">
-        <v>0</v>
       </c>
       <c r="BZ19" s="1">
         <v>0</v>
@@ -1428,10 +1410,10 @@
       <c r="AN20" s="1">
         <v>0</v>
       </c>
-      <c r="AV20" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI20" s="1">
+      <c r="AU20" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="1">
         <v>0</v>
       </c>
       <c r="BZ20" s="1">
@@ -1460,7 +1442,7 @@
       <c r="AM21" s="1">
         <v>5</v>
       </c>
-      <c r="BH21" s="1">
+      <c r="BI21" s="1">
         <v>5</v>
       </c>
       <c r="BZ21" s="1">
@@ -1489,7 +1471,7 @@
       <c r="AL22" s="1">
         <v>0</v>
       </c>
-      <c r="BG22" s="1">
+      <c r="BH22" s="1">
         <v>0</v>
       </c>
       <c r="BZ22" s="1">
@@ -1533,7 +1515,7 @@
       <c r="AK23" s="1">
         <v>0</v>
       </c>
-      <c r="BF23" s="1">
+      <c r="BG23" s="1">
         <v>0</v>
       </c>
       <c r="BZ23" s="1">
@@ -1574,13 +1556,10 @@
       <c r="U24" s="1">
         <v>0</v>
       </c>
-      <c r="V24" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="1">
         <v>5</v>
       </c>
-      <c r="BE24" s="1">
+      <c r="BF24" s="1">
         <v>5</v>
       </c>
       <c r="BZ24" s="1">
@@ -1621,13 +1600,10 @@
       <c r="U25" s="1">
         <v>0</v>
       </c>
-      <c r="W25" s="1">
-        <v>6</v>
-      </c>
       <c r="AI25" s="1">
         <v>0</v>
       </c>
-      <c r="BD25" s="1">
+      <c r="BE25" s="1">
         <v>0</v>
       </c>
       <c r="BZ25" s="1">
@@ -1668,6 +1644,12 @@
       <c r="U26" s="1">
         <v>4</v>
       </c>
+      <c r="V26" s="1">
+        <v>0</v>
+      </c>
+      <c r="W26" s="1">
+        <v>3</v>
+      </c>
       <c r="X26" s="1">
         <v>0</v>
       </c>
@@ -3063,9 +3045,6 @@
       <c r="U47" s="1">
         <v>4</v>
       </c>
-      <c r="AD47" s="1">
-        <v>0</v>
-      </c>
       <c r="AE47" s="1">
         <v>0</v>
       </c>
@@ -3146,9 +3125,6 @@
       <c r="U48" s="1">
         <v>0</v>
       </c>
-      <c r="AC48" s="1">
-        <v>5</v>
-      </c>
       <c r="AE48" s="1">
         <v>0</v>
       </c>
@@ -3248,6 +3224,12 @@
         <v>0</v>
       </c>
       <c r="AB49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD49" s="1">
         <v>0</v>
       </c>
       <c r="AE49" s="1">
@@ -4402,7 +4384,19 @@
       <c r="AE61" s="1">
         <v>4</v>
       </c>
-      <c r="BF61" s="1">
+      <c r="BC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG61" s="3">
         <v>0</v>
       </c>
       <c r="BO61" s="1">
@@ -4440,8 +4434,20 @@
       <c r="AE62" s="1">
         <v>0</v>
       </c>
-      <c r="BF62" s="1">
-        <v>4</v>
+      <c r="BC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG62" s="3">
+        <v>0</v>
       </c>
       <c r="BO62" s="1">
         <v>0</v>
@@ -4478,7 +4484,19 @@
       <c r="AE63" s="1">
         <v>0</v>
       </c>
-      <c r="BF63" s="1">
+      <c r="BC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE63" s="3">
+        <v>11</v>
+      </c>
+      <c r="BF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG63" s="3">
         <v>0</v>
       </c>
       <c r="BO63" s="1">
@@ -4516,7 +4534,19 @@
       <c r="AE64" s="1">
         <v>4</v>
       </c>
-      <c r="BF64" s="1">
+      <c r="BC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG64" s="3">
         <v>0</v>
       </c>
       <c r="BO64" s="1">
@@ -4566,8 +4596,20 @@
       <c r="AE65" s="1">
         <v>0</v>
       </c>
-      <c r="BF65" s="1">
-        <v>4</v>
+      <c r="BC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG65" s="3">
+        <v>0</v>
       </c>
       <c r="BO65" s="1">
         <v>0</v>
@@ -4592,7 +4634,19 @@
       <c r="AE66" s="1">
         <v>0</v>
       </c>
-      <c r="BF66" s="1">
+      <c r="BC66" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD66" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE66" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF66" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG66" s="3">
         <v>0</v>
       </c>
       <c r="BO66" s="1">
@@ -4618,7 +4672,19 @@
       <c r="AE67" s="1">
         <v>4</v>
       </c>
-      <c r="BF67" s="1">
+      <c r="BC67" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD67" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE67" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF67" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG67" s="3">
         <v>0</v>
       </c>
       <c r="BO67" s="1">
@@ -4644,8 +4710,20 @@
       <c r="AE68" s="1">
         <v>0</v>
       </c>
-      <c r="BF68" s="1">
-        <v>4</v>
+      <c r="BC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE68" s="3">
+        <v>11</v>
+      </c>
+      <c r="BF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG68" s="3">
+        <v>0</v>
       </c>
       <c r="BO68" s="1">
         <v>0</v>
@@ -4670,7 +4748,19 @@
       <c r="AE69" s="1">
         <v>0</v>
       </c>
-      <c r="BF69" s="1">
+      <c r="BC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG69" s="3">
         <v>0</v>
       </c>
       <c r="BO69" s="1">
@@ -4711,7 +4801,19 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
-      <c r="BF70" s="1">
+      <c r="BC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG70" s="3">
         <v>0</v>
       </c>
       <c r="BO70" s="1">
@@ -4758,8 +4860,8 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
-      <c r="BF71" s="1">
-        <v>4</v>
+      <c r="BE71" s="1">
+        <v>0</v>
       </c>
       <c r="BO71" s="1">
         <v>0</v>
@@ -4805,8 +4907,8 @@
       <c r="AM72" s="3">
         <v>0</v>
       </c>
-      <c r="BF72" s="1">
-        <v>0</v>
+      <c r="BE72" s="1">
+        <v>4</v>
       </c>
       <c r="BO72" s="1">
         <v>4</v>
@@ -4834,9 +4936,6 @@
       <c r="U73" s="1">
         <v>0</v>
       </c>
-      <c r="V73" s="1">
-        <v>0</v>
-      </c>
       <c r="AE73" s="1">
         <v>4</v>
       </c>
@@ -4855,7 +4954,7 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
-      <c r="BF73" s="1">
+      <c r="BE73" s="1">
         <v>0</v>
       </c>
       <c r="BO73" s="1">
@@ -4902,9 +5001,6 @@
       <c r="U74" s="1">
         <v>4</v>
       </c>
-      <c r="W74" s="1">
-        <v>6</v>
-      </c>
       <c r="AE74" s="1">
         <v>0</v>
       </c>
@@ -4923,8 +5019,20 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
-      <c r="BF74" s="1">
-        <v>4</v>
+      <c r="BC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG74" s="3">
+        <v>0</v>
       </c>
       <c r="BO74" s="1">
         <v>0</v>
@@ -4985,6 +5093,12 @@
       <c r="U75" s="1">
         <v>0</v>
       </c>
+      <c r="V75" s="1">
+        <v>0</v>
+      </c>
+      <c r="W75" s="1">
+        <v>3</v>
+      </c>
       <c r="X75" s="1">
         <v>0</v>
       </c>
@@ -5078,16 +5192,19 @@
       <c r="BB75" s="1">
         <v>0</v>
       </c>
-      <c r="BC75" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD75" s="1">
-        <v>3</v>
-      </c>
-      <c r="BE75" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF75" s="1">
+      <c r="BC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG75" s="3">
         <v>0</v>
       </c>
       <c r="BO75" s="1">
@@ -5122,13 +5239,25 @@
       <c r="AE76" s="1">
         <v>0</v>
       </c>
-      <c r="AT76" s="4">
+      <c r="AS76" s="4">
         <v>0</v>
       </c>
       <c r="AW76" s="4">
         <v>0</v>
       </c>
-      <c r="AZ76" s="4">
+      <c r="BC76" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD76" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE76" s="3">
+        <v>11</v>
+      </c>
+      <c r="BF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG76" s="3">
         <v>0</v>
       </c>
       <c r="BO76" s="1">
@@ -5163,14 +5292,26 @@
       <c r="AE77" s="1">
         <v>4</v>
       </c>
-      <c r="AT77" s="4">
+      <c r="AS77" s="4">
         <v>8</v>
       </c>
       <c r="AW77" s="4">
         <v>8</v>
       </c>
-      <c r="AZ77" s="4">
-        <v>8</v>
+      <c r="BC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG77" s="3">
+        <v>0</v>
       </c>
       <c r="BO77" s="1">
         <v>0</v>
@@ -5198,13 +5339,25 @@
       <c r="AE78" s="1">
         <v>0</v>
       </c>
-      <c r="AT78" s="4">
+      <c r="AS78" s="4">
         <v>0</v>
       </c>
       <c r="AW78" s="4">
         <v>0</v>
       </c>
-      <c r="AZ78" s="4">
+      <c r="BC78" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD78" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE78" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF78" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG78" s="3">
         <v>0</v>
       </c>
       <c r="BO78" s="1">
@@ -5233,13 +5386,13 @@
       <c r="AE79" s="1">
         <v>0</v>
       </c>
-      <c r="AT79" s="4">
+      <c r="AS79" s="4">
         <v>0</v>
       </c>
       <c r="AW79" s="4">
         <v>0</v>
       </c>
-      <c r="AZ79" s="4">
+      <c r="BE79" s="4">
         <v>0</v>
       </c>
       <c r="BO79" s="1">
@@ -5268,13 +5421,13 @@
       <c r="AE80" s="1">
         <v>4</v>
       </c>
-      <c r="AT80" s="4">
+      <c r="AS80" s="4">
         <v>8</v>
       </c>
       <c r="AW80" s="4">
         <v>8</v>
       </c>
-      <c r="AZ80" s="4">
+      <c r="BE80" s="4">
         <v>8</v>
       </c>
       <c r="BO80" s="1">
@@ -5303,13 +5456,13 @@
       <c r="AE81" s="1">
         <v>0</v>
       </c>
-      <c r="AT81" s="4">
+      <c r="AS81" s="4">
         <v>0</v>
       </c>
       <c r="AW81" s="4">
         <v>0</v>
       </c>
-      <c r="AZ81" s="4">
+      <c r="BE81" s="4">
         <v>0</v>
       </c>
       <c r="BO81" s="1">
@@ -5338,13 +5491,13 @@
       <c r="AL82" s="1">
         <v>0</v>
       </c>
-      <c r="AT82" s="4">
+      <c r="AS82" s="4">
         <v>0</v>
       </c>
       <c r="AW82" s="4">
         <v>0</v>
       </c>
-      <c r="AZ82" s="4">
+      <c r="BE82" s="4">
         <v>0</v>
       </c>
       <c r="BO82" s="1">
@@ -5373,13 +5526,13 @@
       <c r="AL83" s="1">
         <v>4</v>
       </c>
-      <c r="AT83" s="4">
+      <c r="AS83" s="4">
         <v>8</v>
       </c>
       <c r="AW83" s="4">
         <v>8</v>
       </c>
-      <c r="AZ83" s="4">
+      <c r="BE83" s="4">
         <v>8</v>
       </c>
       <c r="BO83" s="1">
@@ -5408,13 +5561,13 @@
       <c r="AL84" s="1">
         <v>0</v>
       </c>
-      <c r="AT84" s="4">
+      <c r="AS84" s="4">
         <v>0</v>
       </c>
       <c r="AW84" s="4">
         <v>0</v>
       </c>
-      <c r="AZ84" s="4">
+      <c r="BE84" s="4">
         <v>0</v>
       </c>
       <c r="BO84" s="1">
@@ -5443,13 +5596,13 @@
       <c r="AL85" s="1">
         <v>0</v>
       </c>
-      <c r="AT85" s="4">
+      <c r="AS85" s="4">
         <v>0</v>
       </c>
       <c r="AW85" s="4">
         <v>0</v>
       </c>
-      <c r="AZ85" s="4">
+      <c r="BE85" s="4">
         <v>0</v>
       </c>
       <c r="BO85" s="1">
@@ -5478,13 +5631,13 @@
       <c r="AL86" s="1">
         <v>4</v>
       </c>
-      <c r="AT86" s="4">
+      <c r="AS86" s="4">
         <v>8</v>
       </c>
       <c r="AW86" s="4">
         <v>8</v>
       </c>
-      <c r="AZ86" s="4">
+      <c r="BE86" s="4">
         <v>8</v>
       </c>
       <c r="BM86" s="3">
@@ -5525,13 +5678,13 @@
       <c r="AL87" s="1">
         <v>0</v>
       </c>
-      <c r="AT87" s="4">
+      <c r="AS87" s="4">
         <v>0</v>
       </c>
       <c r="AW87" s="4">
         <v>0</v>
       </c>
-      <c r="AZ87" s="4">
+      <c r="BE87" s="4">
         <v>0</v>
       </c>
       <c r="BM87" s="3">

--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E217DC-E84D-4FD0-B53B-8B4AA06510C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EAA506D6-B2B7-4686-BF2D-F8F0CFFF0508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_3" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -729,16 +729,10 @@
       <c r="E2" s="1">
         <v>5</v>
       </c>
-      <c r="AI2" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ2" s="1">
-        <v>3</v>
-      </c>
-      <c r="AK2" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="1">
         <v>0</v>
       </c>
       <c r="CR2" s="1">
@@ -749,11 +743,11 @@
       <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="AI3" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK3" s="4">
-        <v>8</v>
+      <c r="AJ3" s="1">
+        <v>4</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>4</v>
       </c>
       <c r="CS3" s="1">
         <v>0</v>
@@ -763,10 +757,10 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="AI4" s="1">
-        <v>4</v>
-      </c>
-      <c r="BK4" s="4">
+      <c r="AJ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="1">
         <v>0</v>
       </c>
       <c r="CT4" s="1">
@@ -777,10 +771,10 @@
       <c r="B5" s="1">
         <v>5</v>
       </c>
-      <c r="AI5" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK5" s="4">
+      <c r="AJ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="1">
         <v>0</v>
       </c>
       <c r="CU5" s="1">
@@ -791,11 +785,17 @@
       <c r="A6" s="1">
         <v>0</v>
       </c>
-      <c r="AI6" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK6" s="4">
-        <v>8</v>
+      <c r="AJ6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>4</v>
+      </c>
+      <c r="BK6" s="1">
+        <v>0</v>
       </c>
       <c r="CV6" s="1">
         <v>0</v>
@@ -805,11 +805,17 @@
       <c r="A7" s="1">
         <v>0</v>
       </c>
-      <c r="AI7" s="4">
-        <v>8</v>
-      </c>
-      <c r="BK7" s="4">
-        <v>0</v>
+      <c r="AJ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="1">
+        <v>4</v>
       </c>
       <c r="CV7" s="1">
         <v>0</v>
@@ -819,7 +825,7 @@
       <c r="A8" s="1">
         <v>0</v>
       </c>
-      <c r="AI8" s="4">
+      <c r="AS8" s="1">
         <v>0</v>
       </c>
       <c r="BK8" s="1">
@@ -833,11 +839,11 @@
       <c r="A9" s="1">
         <v>0</v>
       </c>
-      <c r="AI9" s="4">
+      <c r="AS9" s="1">
         <v>0</v>
       </c>
       <c r="BK9" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CG9" s="1">
         <v>0</v>
@@ -853,11 +859,11 @@
       <c r="A10" s="1">
         <v>0</v>
       </c>
-      <c r="AI10" s="4">
-        <v>8</v>
+      <c r="AS10" s="1">
+        <v>4</v>
       </c>
       <c r="BK10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CG10" s="1">
         <v>4</v>
@@ -873,14 +879,8 @@
       <c r="A11" s="1">
         <v>0</v>
       </c>
-      <c r="AI11" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ11" s="1">
-        <v>3</v>
+      <c r="AS11" s="1">
+        <v>0</v>
       </c>
       <c r="BK11" s="1">
         <v>0</v>
@@ -1087,10 +1087,22 @@
       <c r="U13" s="1">
         <v>0</v>
       </c>
-      <c r="BB13" s="1">
-        <v>5</v>
-      </c>
-      <c r="BZ13" s="1">
+      <c r="BA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ13" s="3">
         <v>0</v>
       </c>
       <c r="CA13" s="1">
@@ -1128,11 +1140,23 @@
       <c r="U14" s="1">
         <v>4</v>
       </c>
-      <c r="BA14" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ14" s="1">
-        <v>4</v>
+      <c r="AZ14" s="1">
+        <v>5</v>
+      </c>
+      <c r="BV14" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW14" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX14" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY14" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ14" s="3">
+        <v>0</v>
       </c>
       <c r="CG14" s="1">
         <v>0</v>
@@ -1166,10 +1190,22 @@
       <c r="U15" s="1">
         <v>0</v>
       </c>
-      <c r="AZ15" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ15" s="1">
+      <c r="AY15" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV15" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX15" s="3">
+        <v>11</v>
+      </c>
+      <c r="BY15" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ15" s="3">
         <v>0</v>
       </c>
       <c r="CG15" s="1">
@@ -1204,10 +1240,22 @@
       <c r="U16" s="1">
         <v>0</v>
       </c>
-      <c r="AY16" s="1">
-        <v>5</v>
-      </c>
-      <c r="BZ16" s="1">
+      <c r="AX16" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV16" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW16" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX16" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY16" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ16" s="3">
         <v>0</v>
       </c>
       <c r="CG16" s="1">
@@ -1251,11 +1299,23 @@
       <c r="U17" s="1">
         <v>4</v>
       </c>
-      <c r="AX17" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ17" s="1">
-        <v>4</v>
+      <c r="AW17" s="1">
+        <v>5</v>
+      </c>
+      <c r="BV17" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW17" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX17" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY17" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ17" s="3">
+        <v>0</v>
       </c>
       <c r="CG17" s="1">
         <v>0</v>
@@ -1289,10 +1349,7 @@
       <c r="U18" s="1">
         <v>0</v>
       </c>
-      <c r="AW18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ18" s="1">
+      <c r="AV18" s="1">
         <v>0</v>
       </c>
       <c r="CG18" s="1">
@@ -1327,10 +1384,7 @@
       <c r="U19" s="1">
         <v>0</v>
       </c>
-      <c r="AV19" s="1">
-        <v>5</v>
-      </c>
-      <c r="BZ19" s="1">
+      <c r="AU19" s="1">
         <v>0</v>
       </c>
       <c r="CG19" s="1">
@@ -1407,17 +1461,11 @@
       <c r="U20" s="1">
         <v>4</v>
       </c>
-      <c r="AN20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ20" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ20" s="1">
-        <v>4</v>
+      <c r="AT20" s="1">
+        <v>5</v>
+      </c>
+      <c r="BO20" s="1">
+        <v>0</v>
       </c>
       <c r="CG20" s="1">
         <v>0</v>
@@ -1439,14 +1487,11 @@
       <c r="U21" s="1">
         <v>0</v>
       </c>
-      <c r="AM21" s="1">
-        <v>5</v>
-      </c>
-      <c r="BI21" s="1">
-        <v>5</v>
-      </c>
-      <c r="BZ21" s="1">
-        <v>0</v>
+      <c r="AS21" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO21" s="1">
+        <v>4</v>
       </c>
       <c r="CG21" s="1">
         <v>0</v>
@@ -1468,13 +1513,7 @@
       <c r="U22" s="1">
         <v>0</v>
       </c>
-      <c r="AL22" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH22" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ22" s="1">
+      <c r="BO22" s="1">
         <v>0</v>
       </c>
       <c r="CG22" s="1">
@@ -1512,14 +1551,11 @@
       <c r="U23" s="1">
         <v>4</v>
       </c>
-      <c r="AK23" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG23" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ23" s="1">
-        <v>4</v>
+      <c r="AE23" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO23" s="1">
+        <v>0</v>
       </c>
       <c r="CG23" s="1">
         <v>0</v>
@@ -1556,14 +1592,11 @@
       <c r="U24" s="1">
         <v>0</v>
       </c>
-      <c r="AJ24" s="1">
-        <v>5</v>
-      </c>
-      <c r="BF24" s="1">
-        <v>5</v>
-      </c>
-      <c r="BZ24" s="1">
-        <v>0</v>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO24" s="1">
+        <v>4</v>
       </c>
       <c r="CG24" s="1">
         <v>0</v>
@@ -1600,13 +1633,10 @@
       <c r="U25" s="1">
         <v>0</v>
       </c>
-      <c r="AI25" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE25" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ25" s="1">
+      <c r="AE25" s="1">
+        <v>4</v>
+      </c>
+      <c r="BO25" s="1">
         <v>0</v>
       </c>
       <c r="CG25" s="1">
@@ -1644,31 +1674,19 @@
       <c r="U26" s="1">
         <v>4</v>
       </c>
-      <c r="V26" s="1">
-        <v>0</v>
-      </c>
-      <c r="W26" s="1">
-        <v>3</v>
-      </c>
-      <c r="X26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="4">
-        <v>7</v>
-      </c>
-      <c r="AA26" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="4">
-        <v>7</v>
-      </c>
-      <c r="AD26" s="4">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>0</v>
       </c>
       <c r="AE26" s="1">
@@ -1781,9 +1799,6 @@
       </c>
       <c r="BO26" s="1">
         <v>0</v>
-      </c>
-      <c r="BZ26" s="1">
-        <v>4</v>
       </c>
       <c r="CG26" s="1">
         <v>0</v>
@@ -1820,17 +1835,26 @@
       <c r="U27" s="1">
         <v>0</v>
       </c>
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
       <c r="AE27" s="1">
         <v>0</v>
       </c>
-      <c r="BI27" s="4">
-        <v>0</v>
-      </c>
       <c r="BO27" s="1">
         <v>4</v>
-      </c>
-      <c r="BZ27" s="1">
-        <v>0</v>
       </c>
       <c r="CV27" s="1">
         <v>0</v>
@@ -1846,16 +1870,25 @@
       <c r="U28" s="1">
         <v>0</v>
       </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>11</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
       <c r="AE28" s="1">
         <v>4</v>
       </c>
-      <c r="BI28" s="4">
-        <v>8</v>
-      </c>
       <c r="BO28" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ28" s="1">
         <v>0</v>
       </c>
       <c r="CV28" s="1">
@@ -1872,17 +1905,23 @@
       <c r="U29" s="1">
         <v>4</v>
       </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
       <c r="AE29" s="1">
         <v>0</v>
-      </c>
-      <c r="BI29" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO29" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ29" s="1">
-        <v>4</v>
       </c>
       <c r="CV29" s="1">
         <v>0</v>
@@ -1898,31 +1937,22 @@
       <c r="U30" s="1">
         <v>0</v>
       </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
       <c r="AE30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AV30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO30" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ30" s="1">
         <v>0</v>
       </c>
       <c r="CV30" s="1">
@@ -1942,30 +1972,6 @@
       <c r="AE31" s="1">
         <v>4</v>
       </c>
-      <c r="AV31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="4">
-        <v>8</v>
-      </c>
-      <c r="BO31" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ31" s="1">
-        <v>0</v>
-      </c>
       <c r="CV31" s="1">
         <v>0</v>
       </c>
@@ -1995,45 +2001,6 @@
       <c r="AE32" s="1">
         <v>0</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX32" s="3">
-        <v>11</v>
-      </c>
-      <c r="AY32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO32" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ32" s="1">
-        <v>4</v>
-      </c>
       <c r="CV32" s="1">
         <v>0</v>
       </c>
@@ -2063,63 +2030,6 @@
       <c r="AE33" s="1">
         <v>0</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI33" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ33" s="1">
-        <v>3</v>
-      </c>
-      <c r="BK33" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL33" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM33" s="1">
-        <v>3</v>
-      </c>
-      <c r="BN33" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO33" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ33" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG33" s="1">
-        <v>0</v>
-      </c>
       <c r="CM33" s="1">
         <v>0</v>
       </c>
@@ -2152,45 +2062,6 @@
       <c r="AE34" s="1">
         <v>4</v>
       </c>
-      <c r="AF34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="3">
-        <v>11</v>
-      </c>
-      <c r="AI34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO34" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ34" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG34" s="1">
-        <v>4</v>
-      </c>
       <c r="CM34" s="1">
         <v>4</v>
       </c>
@@ -2223,30 +2094,6 @@
       <c r="AE35" s="1">
         <v>0</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO35" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ35" s="1">
-        <v>4</v>
-      </c>
-      <c r="CG35" s="1">
-        <v>0</v>
-      </c>
       <c r="CM35" s="1">
         <v>0</v>
       </c>
@@ -2279,28 +2126,19 @@
       <c r="AE36" s="1">
         <v>0</v>
       </c>
-      <c r="AF36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO36" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ36" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG36" s="1">
+      <c r="BW36" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX36" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY36" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ36" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA36" s="3">
         <v>0</v>
       </c>
       <c r="CM36" s="1">
@@ -2323,14 +2161,20 @@
       <c r="AE37" s="1">
         <v>4</v>
       </c>
-      <c r="BO37" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ37" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG37" s="1">
-        <v>4</v>
+      <c r="BW37" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX37" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY37" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ37" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA37" s="3">
+        <v>0</v>
       </c>
       <c r="CM37" s="1">
         <v>4</v>
@@ -2352,13 +2196,19 @@
       <c r="AE38" s="1">
         <v>0</v>
       </c>
-      <c r="BO38" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ38" s="1">
-        <v>4</v>
-      </c>
-      <c r="CG38" s="1">
+      <c r="BW38" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX38" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY38" s="3">
+        <v>11</v>
+      </c>
+      <c r="BZ38" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA38" s="3">
         <v>0</v>
       </c>
       <c r="CM38" s="1">
@@ -2381,13 +2231,19 @@
       <c r="AE39" s="1">
         <v>0</v>
       </c>
-      <c r="BO39" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ39" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG39" s="1">
+      <c r="BW39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ39" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA39" s="3">
         <v>0</v>
       </c>
       <c r="CM39" s="1">
@@ -2410,14 +2266,20 @@
       <c r="AE40" s="1">
         <v>4</v>
       </c>
-      <c r="BO40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ40" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG40" s="1">
-        <v>4</v>
+      <c r="BW40" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX40" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY40" s="3">
+        <v>0</v>
+      </c>
+      <c r="BZ40" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA40" s="3">
+        <v>0</v>
       </c>
       <c r="CM40" s="1">
         <v>4</v>
@@ -2439,75 +2301,6 @@
       <c r="AE41" s="1">
         <v>0</v>
       </c>
-      <c r="AN41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY41" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG41" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO41" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ41" s="1">
-        <v>4</v>
-      </c>
-      <c r="CG41" s="1">
-        <v>0</v>
-      </c>
       <c r="CM41" s="1">
         <v>0</v>
       </c>
@@ -2588,15 +2381,6 @@
       <c r="BG42" s="2">
         <v>0</v>
       </c>
-      <c r="BO42" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ42" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG42" s="1">
-        <v>0</v>
-      </c>
       <c r="CM42" s="1">
         <v>0</v>
       </c>
@@ -2608,6 +2392,18 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
+      <c r="C43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
       <c r="K43" s="1">
         <v>0</v>
       </c>
@@ -2676,15 +2472,6 @@
       </c>
       <c r="BG43" s="2">
         <v>0</v>
-      </c>
-      <c r="BO43" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ43" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG43" s="1">
-        <v>4</v>
       </c>
       <c r="CM43" s="1">
         <v>4</v>
@@ -2697,32 +2484,17 @@
       <c r="A44" s="1">
         <v>0</v>
       </c>
-      <c r="B44" s="4">
-        <v>0</v>
-      </c>
-      <c r="C44" s="4">
-        <v>7</v>
-      </c>
-      <c r="D44" s="4">
-        <v>0</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4">
-        <v>7</v>
-      </c>
-      <c r="G44" s="4">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
+      <c r="C44" s="1">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1">
+        <v>4</v>
+      </c>
+      <c r="G44" s="1">
+        <v>4</v>
       </c>
       <c r="I44" s="1">
-        <v>3</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" s="1">
         <v>4</v>
@@ -2791,15 +2563,6 @@
         <v>0</v>
       </c>
       <c r="BG44" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ44" s="1">
-        <v>4</v>
-      </c>
-      <c r="CG44" s="1">
         <v>0</v>
       </c>
       <c r="CM44" s="1">
@@ -2813,6 +2576,18 @@
       <c r="A45" s="1">
         <v>0</v>
       </c>
+      <c r="C45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
       <c r="K45" s="1">
         <v>0</v>
       </c>
@@ -2880,30 +2655,6 @@
         <v>0</v>
       </c>
       <c r="BG45" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO45" s="1">
-        <v>4</v>
-      </c>
-      <c r="BZ45" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA45" s="1">
-        <v>0</v>
-      </c>
-      <c r="CB45" s="1">
-        <v>3</v>
-      </c>
-      <c r="CC45" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD45" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE45" s="1">
-        <v>3</v>
-      </c>
-      <c r="CF45" s="1">
         <v>0</v>
       </c>
       <c r="CM45" s="1">
@@ -2941,30 +2692,27 @@
       <c r="A46" s="1">
         <v>0</v>
       </c>
-      <c r="B46" s="1">
-        <v>0</v>
-      </c>
-      <c r="C46" s="1">
-        <v>4</v>
-      </c>
-      <c r="D46" s="1">
-        <v>0</v>
-      </c>
-      <c r="F46" s="1">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>4</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
       <c r="K46" s="1">
         <v>0</v>
       </c>
       <c r="U46" s="1">
         <v>0</v>
       </c>
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
       <c r="AE46" s="1">
         <v>4</v>
       </c>
@@ -3026,9 +2774,6 @@
         <v>0</v>
       </c>
       <c r="BG46" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO46" s="1">
         <v>0</v>
       </c>
       <c r="CV46" s="1">
@@ -3045,6 +2790,21 @@
       <c r="U47" s="1">
         <v>4</v>
       </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
       <c r="AE47" s="1">
         <v>0</v>
       </c>
@@ -3106,9 +2866,6 @@
         <v>0</v>
       </c>
       <c r="BG47" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO47" s="1">
         <v>0</v>
       </c>
       <c r="CV47" s="1">
@@ -3125,6 +2882,21 @@
       <c r="U48" s="1">
         <v>0</v>
       </c>
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>11</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
       <c r="AE48" s="1">
         <v>0</v>
       </c>
@@ -3187,9 +2959,6 @@
       </c>
       <c r="BG48" s="2">
         <v>0</v>
-      </c>
-      <c r="BO48" s="1">
-        <v>4</v>
       </c>
       <c r="CV48" s="1">
         <v>0</v>
@@ -3205,31 +2974,19 @@
       <c r="U49" s="1">
         <v>0</v>
       </c>
-      <c r="V49" s="4">
-        <v>0</v>
-      </c>
-      <c r="W49" s="4">
-        <v>7</v>
-      </c>
-      <c r="X49" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="4">
-        <v>7</v>
-      </c>
-      <c r="AA49" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="1">
-        <v>3</v>
-      </c>
-      <c r="AD49" s="1">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
         <v>0</v>
       </c>
       <c r="AE49" s="1">
@@ -3293,9 +3050,6 @@
         <v>0</v>
       </c>
       <c r="BG49" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO49" s="1">
         <v>0</v>
       </c>
       <c r="CV49" s="1">
@@ -3312,6 +3066,21 @@
       <c r="U50" s="1">
         <v>4</v>
       </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
       <c r="AE50" s="1">
         <v>0</v>
       </c>
@@ -3346,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="AX50" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY50" s="2">
         <v>0</v>
@@ -3373,9 +3142,6 @@
         <v>0</v>
       </c>
       <c r="BG50" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO50" s="1">
         <v>0</v>
       </c>
       <c r="CV50">
@@ -3438,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="AX51" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY51" s="2">
         <v>0</v>
@@ -3466,9 +3232,6 @@
       </c>
       <c r="BG51" s="2">
         <v>0</v>
-      </c>
-      <c r="BO51" s="1">
-        <v>4</v>
       </c>
       <c r="CV51" s="1">
         <v>0</v>
@@ -3559,9 +3322,6 @@
       <c r="BG52" s="2">
         <v>0</v>
       </c>
-      <c r="BO52" s="1">
-        <v>0</v>
-      </c>
       <c r="CV52" s="1">
         <v>0</v>
       </c>
@@ -3651,9 +3411,6 @@
       <c r="BG53" s="2">
         <v>0</v>
       </c>
-      <c r="BO53" s="1">
-        <v>0</v>
-      </c>
       <c r="CV53" s="1">
         <v>0</v>
       </c>
@@ -3743,9 +3500,6 @@
       <c r="BG54" s="2">
         <v>0</v>
       </c>
-      <c r="BO54" s="1">
-        <v>4</v>
-      </c>
       <c r="CV54" s="1">
         <v>0</v>
       </c>
@@ -3835,27 +3589,6 @@
       <c r="BG55" s="2">
         <v>0</v>
       </c>
-      <c r="BO55" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR55" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS55" s="4">
-        <v>7</v>
-      </c>
-      <c r="BT55" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU55" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV55" s="4">
-        <v>7</v>
-      </c>
-      <c r="BW55" s="4">
-        <v>0</v>
-      </c>
       <c r="BZ55" s="1">
         <v>0</v>
       </c>
@@ -3981,15 +3714,6 @@
       <c r="BG56" s="2">
         <v>0</v>
       </c>
-      <c r="BO56" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR56" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW56" s="1">
-        <v>0</v>
-      </c>
       <c r="BZ56" s="1">
         <v>4</v>
       </c>
@@ -4076,15 +3800,6 @@
       <c r="BG57" s="2">
         <v>0</v>
       </c>
-      <c r="BO57" s="1">
-        <v>4</v>
-      </c>
-      <c r="BQ57" s="1">
-        <v>5</v>
-      </c>
-      <c r="BX57" s="1">
-        <v>6</v>
-      </c>
       <c r="BZ57" s="1">
         <v>0</v>
       </c>
@@ -4171,15 +3886,6 @@
       <c r="BG58" s="2">
         <v>0</v>
       </c>
-      <c r="BO58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY58" s="1">
-        <v>0</v>
-      </c>
       <c r="BZ58" s="1">
         <v>0</v>
       </c>
@@ -4266,9 +3972,6 @@
       <c r="BG59" s="2">
         <v>0</v>
       </c>
-      <c r="BO59" s="1">
-        <v>0</v>
-      </c>
       <c r="BZ59" s="1">
         <v>4</v>
       </c>
@@ -4355,9 +4058,6 @@
       <c r="BG60" s="2">
         <v>0</v>
       </c>
-      <c r="BO60" s="1">
-        <v>4</v>
-      </c>
       <c r="BZ60" s="1">
         <v>0</v>
       </c>
@@ -4384,28 +4084,82 @@
       <c r="AE61" s="1">
         <v>4</v>
       </c>
-      <c r="BC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO61" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP61" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY61" s="1">
+      <c r="AN61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG61" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS61" s="4">
+        <v>7</v>
+      </c>
+      <c r="BT61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV61" s="4">
+        <v>7</v>
+      </c>
+      <c r="BW61" s="4">
         <v>0</v>
       </c>
       <c r="BZ61" s="1">
@@ -4434,29 +4188,11 @@
       <c r="AE62" s="1">
         <v>0</v>
       </c>
-      <c r="BC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD62" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE62" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF62" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG62" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO62" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ62" s="1">
-        <v>6</v>
-      </c>
-      <c r="BX62" s="1">
-        <v>5</v>
+      <c r="BR62" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW62" s="1">
+        <v>0</v>
       </c>
       <c r="BZ62" s="1">
         <v>4</v>
@@ -4484,29 +4220,11 @@
       <c r="AE63" s="1">
         <v>0</v>
       </c>
-      <c r="BC63" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD63" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE63" s="3">
-        <v>11</v>
-      </c>
-      <c r="BF63" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG63" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO63" s="1">
-        <v>4</v>
-      </c>
-      <c r="BR63" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW63" s="1">
-        <v>0</v>
+      <c r="BQ63" s="1">
+        <v>5</v>
+      </c>
+      <c r="BX63" s="1">
+        <v>6</v>
       </c>
       <c r="BZ63" s="1">
         <v>0</v>
@@ -4534,40 +4252,13 @@
       <c r="AE64" s="1">
         <v>4</v>
       </c>
-      <c r="BC64" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD64" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE64" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF64" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG64" s="3">
-        <v>0</v>
-      </c>
       <c r="BO64" s="1">
         <v>0</v>
       </c>
-      <c r="BR64" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS64" s="4">
-        <v>7</v>
-      </c>
-      <c r="BT64" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU64" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV64" s="4">
-        <v>7</v>
-      </c>
-      <c r="BW64" s="4">
+      <c r="BP64" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY64" s="1">
         <v>0</v>
       </c>
       <c r="BZ64" s="1">
@@ -4596,26 +4287,17 @@
       <c r="AE65" s="1">
         <v>0</v>
       </c>
-      <c r="BC65" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD65" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE65" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF65" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG65" s="3">
-        <v>0</v>
-      </c>
       <c r="BO65" s="1">
         <v>0</v>
       </c>
       <c r="BZ65" s="1">
         <v>4</v>
+      </c>
+      <c r="CG65" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM65" s="1">
+        <v>0</v>
       </c>
       <c r="CV65" s="1">
         <v>0</v>
@@ -4634,26 +4316,17 @@
       <c r="AE66" s="1">
         <v>0</v>
       </c>
-      <c r="BC66" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD66" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE66" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF66" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG66" s="3">
-        <v>0</v>
-      </c>
       <c r="BO66" s="1">
         <v>4</v>
       </c>
       <c r="BZ66" s="1">
         <v>0</v>
+      </c>
+      <c r="CG66" s="1">
+        <v>4</v>
+      </c>
+      <c r="CM66" s="1">
+        <v>4</v>
       </c>
       <c r="CV66" s="1">
         <v>0</v>
@@ -4669,28 +4342,40 @@
       <c r="U67" s="1">
         <v>0</v>
       </c>
+      <c r="V67" s="3">
+        <v>0</v>
+      </c>
+      <c r="W67" s="3">
+        <v>0</v>
+      </c>
+      <c r="X67" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="3">
+        <v>0</v>
+      </c>
       <c r="AE67" s="1">
         <v>4</v>
       </c>
-      <c r="BC67" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD67" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE67" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF67" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG67" s="3">
-        <v>0</v>
-      </c>
       <c r="BO67" s="1">
         <v>0</v>
       </c>
+      <c r="BP67" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY67" s="1">
+        <v>0</v>
+      </c>
       <c r="BZ67" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG67" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM67" s="1">
         <v>0</v>
       </c>
       <c r="CV67" s="1">
@@ -4707,29 +4392,41 @@
       <c r="U68" s="1">
         <v>4</v>
       </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
       <c r="AE68" s="1">
         <v>0</v>
       </c>
-      <c r="BC68" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD68" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE68" s="3">
-        <v>11</v>
-      </c>
-      <c r="BF68" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG68" s="3">
-        <v>0</v>
-      </c>
       <c r="BO68" s="1">
         <v>0</v>
       </c>
+      <c r="BQ68" s="1">
+        <v>6</v>
+      </c>
+      <c r="BX68" s="1">
+        <v>5</v>
+      </c>
       <c r="BZ68" s="1">
         <v>4</v>
+      </c>
+      <c r="CG68" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM68" s="1">
+        <v>0</v>
       </c>
       <c r="CV68" s="1">
         <v>0</v>
@@ -4745,29 +4442,41 @@
       <c r="U69" s="1">
         <v>0</v>
       </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>11</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
       <c r="AE69" s="1">
         <v>0</v>
       </c>
-      <c r="BC69" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD69" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE69" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF69" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG69" s="3">
-        <v>0</v>
-      </c>
       <c r="BO69" s="1">
         <v>4</v>
       </c>
+      <c r="BR69" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW69" s="1">
+        <v>0</v>
+      </c>
       <c r="BZ69" s="1">
         <v>0</v>
+      </c>
+      <c r="CG69" s="1">
+        <v>4</v>
+      </c>
+      <c r="CM69" s="1">
+        <v>4</v>
       </c>
       <c r="CV69" s="1">
         <v>0</v>
@@ -4783,40 +4492,43 @@
       <c r="U70" s="1">
         <v>0</v>
       </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
       <c r="AE70" s="1">
         <v>4</v>
       </c>
-      <c r="AI70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM70" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC70" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD70" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE70" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF70" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG70" s="3">
-        <v>0</v>
-      </c>
       <c r="BO70" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR70" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS70" s="4">
+        <v>7</v>
+      </c>
+      <c r="BT70" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU70" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV70" s="4">
+        <v>7</v>
+      </c>
+      <c r="BW70" s="4">
         <v>0</v>
       </c>
       <c r="BZ70" s="1">
@@ -4842,27 +4554,24 @@
       <c r="U71" s="1">
         <v>4</v>
       </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
       <c r="AE71" s="1">
         <v>0</v>
       </c>
-      <c r="AI71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM71" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE71" s="1">
-        <v>0</v>
-      </c>
       <c r="BO71" s="1">
         <v>0</v>
       </c>
@@ -4870,10 +4579,10 @@
         <v>4</v>
       </c>
       <c r="CG71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CM71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV71" s="1">
         <v>0</v>
@@ -4892,24 +4601,6 @@
       <c r="AE72" s="1">
         <v>0</v>
       </c>
-      <c r="AI72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK72" s="3">
-        <v>11</v>
-      </c>
-      <c r="AL72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM72" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE72" s="1">
-        <v>4</v>
-      </c>
       <c r="BO72" s="1">
         <v>4</v>
       </c>
@@ -4917,10 +4608,10 @@
         <v>0</v>
       </c>
       <c r="CG72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CM72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV72" s="1">
         <v>0</v>
@@ -4939,43 +4630,7 @@
       <c r="AE73" s="1">
         <v>4</v>
       </c>
-      <c r="AI73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM73" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE73" s="1">
-        <v>0</v>
-      </c>
       <c r="BO73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR73" s="4">
-        <v>0</v>
-      </c>
-      <c r="BS73" s="4">
-        <v>7</v>
-      </c>
-      <c r="BT73" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU73" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV73" s="4">
-        <v>7</v>
-      </c>
-      <c r="BW73" s="4">
         <v>0</v>
       </c>
       <c r="BZ73" s="1">
@@ -5004,52 +4659,10 @@
       <c r="AE74" s="1">
         <v>0</v>
       </c>
-      <c r="AI74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM74" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC74" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD74" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE74" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF74" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG74" s="3">
-        <v>0</v>
-      </c>
       <c r="BO74" s="1">
         <v>0</v>
       </c>
-      <c r="BR74" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW74" s="1">
-        <v>0</v>
-      </c>
       <c r="BZ74" s="1">
-        <v>4</v>
-      </c>
-      <c r="CG74" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM74" s="1">
         <v>4</v>
       </c>
       <c r="CV74" s="1">
@@ -5093,136 +4706,13 @@
       <c r="U75" s="1">
         <v>0</v>
       </c>
-      <c r="V75" s="1">
-        <v>0</v>
-      </c>
-      <c r="W75" s="1">
-        <v>3</v>
-      </c>
-      <c r="X75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="4">
-        <v>7</v>
-      </c>
-      <c r="AA75" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC75" s="4">
-        <v>7</v>
-      </c>
-      <c r="AD75" s="4">
-        <v>0</v>
-      </c>
       <c r="AE75" s="1">
         <v>0</v>
       </c>
-      <c r="AF75" s="1">
-        <v>3</v>
-      </c>
-      <c r="AG75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI75" s="1">
-        <v>3</v>
-      </c>
-      <c r="AJ75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL75" s="1">
-        <v>3</v>
-      </c>
-      <c r="AM75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO75" s="1">
-        <v>3</v>
-      </c>
-      <c r="AP75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR75" s="1">
-        <v>3</v>
-      </c>
-      <c r="AS75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AT75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU75" s="1">
-        <v>3</v>
-      </c>
-      <c r="AV75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX75" s="1">
-        <v>3</v>
-      </c>
-      <c r="AY75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ75" s="1">
-        <v>0</v>
-      </c>
-      <c r="BA75" s="1">
-        <v>3</v>
-      </c>
-      <c r="BB75" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC75" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD75" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE75" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF75" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG75" s="3">
-        <v>0</v>
-      </c>
       <c r="BO75" s="1">
         <v>4</v>
       </c>
-      <c r="BQ75" s="1">
-        <v>5</v>
-      </c>
-      <c r="BX75" s="1">
-        <v>6</v>
-      </c>
       <c r="BZ75" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG75" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM75" s="1">
         <v>0</v>
       </c>
       <c r="CV75" s="1">
@@ -5237,45 +4727,12 @@
         <v>0</v>
       </c>
       <c r="AE76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS76" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW76" s="4">
-        <v>0</v>
-      </c>
-      <c r="BC76" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD76" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE76" s="3">
-        <v>11</v>
-      </c>
-      <c r="BF76" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG76" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BO76" s="1">
         <v>0</v>
       </c>
-      <c r="BP76" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY76" s="1">
-        <v>0</v>
-      </c>
       <c r="BZ76" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG76" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM76" s="1">
         <v>0</v>
       </c>
       <c r="CV76" s="1">
@@ -5290,39 +4747,12 @@
         <v>4</v>
       </c>
       <c r="AE77" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS77" s="4">
-        <v>8</v>
-      </c>
-      <c r="AW77" s="4">
-        <v>8</v>
-      </c>
-      <c r="BC77" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD77" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE77" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF77" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG77" s="3">
         <v>0</v>
       </c>
       <c r="BO77" s="1">
         <v>0</v>
       </c>
       <c r="BZ77" s="1">
-        <v>4</v>
-      </c>
-      <c r="CG77" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM77" s="1">
         <v>4</v>
       </c>
       <c r="CV77" s="1">
@@ -5336,40 +4766,25 @@
       <c r="U78" s="1">
         <v>0</v>
       </c>
-      <c r="AE78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS78" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW78" s="4">
-        <v>0</v>
-      </c>
-      <c r="BC78" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD78" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE78" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF78" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG78" s="3">
-        <v>0</v>
-      </c>
       <c r="BO78" s="1">
         <v>4</v>
       </c>
       <c r="BZ78" s="1">
         <v>0</v>
       </c>
-      <c r="CG78" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM78" s="1">
+      <c r="CQ78" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR78" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS78" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT78" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU78" s="3">
         <v>0</v>
       </c>
       <c r="CV78" s="1">
@@ -5383,28 +4798,25 @@
       <c r="U79" s="1">
         <v>0</v>
       </c>
-      <c r="AE79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS79" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW79" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE79" s="4">
-        <v>0</v>
-      </c>
       <c r="BO79" s="1">
         <v>0</v>
       </c>
       <c r="BZ79" s="1">
         <v>0</v>
       </c>
-      <c r="CG79" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM79" s="1">
+      <c r="CQ79" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR79" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS79" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT79" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU79" s="3">
         <v>0</v>
       </c>
       <c r="CV79" s="1">
@@ -5418,29 +4830,26 @@
       <c r="U80" s="1">
         <v>4</v>
       </c>
-      <c r="AE80" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS80" s="4">
-        <v>8</v>
-      </c>
-      <c r="AW80" s="4">
-        <v>8</v>
-      </c>
-      <c r="BE80" s="4">
-        <v>8</v>
-      </c>
       <c r="BO80" s="1">
         <v>0</v>
       </c>
       <c r="BZ80" s="1">
         <v>4</v>
       </c>
-      <c r="CG80" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM80" s="1">
-        <v>4</v>
+      <c r="CQ80" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR80" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS80" s="3">
+        <v>11</v>
+      </c>
+      <c r="CT80" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU80" s="3">
+        <v>0</v>
       </c>
       <c r="CV80" s="1">
         <v>0</v>
@@ -5453,28 +4862,25 @@
       <c r="U81" s="1">
         <v>0</v>
       </c>
-      <c r="AE81" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS81" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW81" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE81" s="4">
-        <v>0</v>
-      </c>
       <c r="BO81" s="1">
         <v>4</v>
       </c>
       <c r="BZ81" s="1">
         <v>0</v>
       </c>
-      <c r="CG81" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM81" s="1">
+      <c r="CQ81" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR81" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS81" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT81" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU81" s="3">
         <v>0</v>
       </c>
       <c r="CV81" s="1">
@@ -5488,28 +4894,40 @@
       <c r="U82" s="1">
         <v>0</v>
       </c>
-      <c r="AL82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS82" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW82" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE82" s="4">
-        <v>0</v>
-      </c>
       <c r="BO82" s="1">
         <v>0</v>
       </c>
       <c r="BZ82" s="1">
         <v>0</v>
       </c>
-      <c r="CG82" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM82" s="1">
+      <c r="CE82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CF82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CQ82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU82" s="3">
         <v>0</v>
       </c>
       <c r="CV82" s="1">
@@ -5523,29 +4941,26 @@
       <c r="U83" s="1">
         <v>4</v>
       </c>
-      <c r="AL83" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS83" s="4">
-        <v>8</v>
-      </c>
-      <c r="AW83" s="4">
-        <v>8</v>
-      </c>
-      <c r="BE83" s="4">
-        <v>8</v>
-      </c>
       <c r="BO83" s="1">
         <v>0</v>
       </c>
       <c r="BZ83" s="1">
         <v>4</v>
       </c>
-      <c r="CG83" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM83" s="1">
-        <v>4</v>
+      <c r="CE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI83" s="3">
+        <v>0</v>
       </c>
       <c r="CV83" s="1">
         <v>0</v>
@@ -5558,28 +4973,25 @@
       <c r="U84" s="1">
         <v>0</v>
       </c>
-      <c r="AL84" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS84" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW84" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE84" s="4">
-        <v>0</v>
-      </c>
       <c r="BO84" s="1">
         <v>4</v>
       </c>
       <c r="BZ84" s="1">
         <v>0</v>
       </c>
-      <c r="CG84" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM84" s="1">
+      <c r="CE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG84" s="3">
+        <v>11</v>
+      </c>
+      <c r="CH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI84" s="3">
         <v>0</v>
       </c>
       <c r="CV84" s="1">
@@ -5593,28 +5005,25 @@
       <c r="U85" s="1">
         <v>0</v>
       </c>
-      <c r="AL85" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS85" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW85" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE85" s="4">
-        <v>0</v>
-      </c>
       <c r="BO85" s="1">
         <v>0</v>
       </c>
       <c r="BZ85" s="1">
         <v>0</v>
       </c>
-      <c r="CG85" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM85" s="1">
+      <c r="CE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="CF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI85" s="3">
         <v>0</v>
       </c>
       <c r="CV85" s="1">
@@ -5628,18 +5037,6 @@
       <c r="U86" s="1">
         <v>4</v>
       </c>
-      <c r="AL86" s="1">
-        <v>4</v>
-      </c>
-      <c r="AS86" s="4">
-        <v>8</v>
-      </c>
-      <c r="AW86" s="4">
-        <v>8</v>
-      </c>
-      <c r="BE86" s="4">
-        <v>8</v>
-      </c>
       <c r="BM86" s="3">
         <v>0</v>
       </c>
@@ -5658,11 +5055,20 @@
       <c r="BZ86" s="1">
         <v>4</v>
       </c>
-      <c r="CG86" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM86" s="1">
-        <v>4</v>
+      <c r="CE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI86" s="3">
+        <v>0</v>
       </c>
       <c r="CV86" s="1">
         <v>0</v>
@@ -5675,18 +5081,6 @@
       <c r="U87" s="1">
         <v>0</v>
       </c>
-      <c r="AL87" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS87" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW87" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE87" s="4">
-        <v>0</v>
-      </c>
       <c r="BM87" s="3">
         <v>0</v>
       </c>
@@ -5703,27 +5097,6 @@
         <v>0</v>
       </c>
       <c r="BZ87" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG87" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM87" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ87" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR87" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS87" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT87" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU87" s="3">
         <v>0</v>
       </c>
       <c r="CV87" s="1">
@@ -5965,45 +5338,6 @@
       <c r="BZ88" s="1">
         <v>0</v>
       </c>
-      <c r="CA88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB88" s="4">
-        <v>7</v>
-      </c>
-      <c r="CC88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE88" s="4">
-        <v>7</v>
-      </c>
-      <c r="CF88" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG88" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM88" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ88" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR88" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS88" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT88" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU88" s="3">
-        <v>0</v>
-      </c>
       <c r="CV88" s="1">
         <v>0</v>
       </c>
@@ -6030,36 +5364,6 @@
       <c r="BQ89" s="3">
         <v>0</v>
       </c>
-      <c r="CG89" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM89" s="1">
-        <v>4</v>
-      </c>
-      <c r="CN89" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO89" s="4">
-        <v>7</v>
-      </c>
-      <c r="CP89" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ89" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR89" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS89" s="3">
-        <v>11</v>
-      </c>
-      <c r="CT89" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU89" s="3">
-        <v>0</v>
-      </c>
       <c r="CV89" s="1">
         <v>0</v>
       </c>
@@ -6086,27 +5390,6 @@
       <c r="BQ90" s="3">
         <v>0</v>
       </c>
-      <c r="CG90" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM90" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ90" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR90" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS90" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT90" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU90" s="3">
-        <v>0</v>
-      </c>
       <c r="CV90" s="1">
         <v>0</v>
       </c>
@@ -6118,27 +5401,6 @@
       <c r="AX91" s="1">
         <v>0</v>
       </c>
-      <c r="CG91" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM91" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ91" s="3">
-        <v>0</v>
-      </c>
-      <c r="CR91" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS91" s="3">
-        <v>0</v>
-      </c>
-      <c r="CT91" s="3">
-        <v>0</v>
-      </c>
-      <c r="CU91" s="3">
-        <v>0</v>
-      </c>
       <c r="CV91" s="1">
         <v>0</v>
       </c>
@@ -6162,12 +5424,6 @@
       <c r="AZ92" s="3">
         <v>0</v>
       </c>
-      <c r="CG92" s="1">
-        <v>4</v>
-      </c>
-      <c r="CM92" s="1">
-        <v>4</v>
-      </c>
       <c r="CV92" s="1">
         <v>0</v>
       </c>
@@ -6189,12 +5445,6 @@
         <v>0</v>
       </c>
       <c r="AZ93" s="3">
-        <v>0</v>
-      </c>
-      <c r="CG93" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM93" s="1">
         <v>0</v>
       </c>
       <c r="CV93" s="1">
@@ -6578,5 +5828,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/media/Levels/Level_3.xlsx
+++ b/media/Levels/Level_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EAA506D6-B2B7-4686-BF2D-F8F0CFFF0508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2C7CD5ED-CB5F-48FD-87C5-3D92D08F32FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
@@ -1464,7 +1464,7 @@
       <c r="AT20" s="1">
         <v>5</v>
       </c>
-      <c r="BO20" s="1">
+      <c r="BP20" s="1">
         <v>0</v>
       </c>
       <c r="CG20" s="1">
@@ -1490,7 +1490,7 @@
       <c r="AS21" s="1">
         <v>0</v>
       </c>
-      <c r="BO21" s="1">
+      <c r="BP21" s="1">
         <v>4</v>
       </c>
       <c r="CG21" s="1">
@@ -1513,7 +1513,10 @@
       <c r="U22" s="1">
         <v>0</v>
       </c>
-      <c r="BO22" s="1">
+      <c r="AE22" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP22" s="1">
         <v>0</v>
       </c>
       <c r="CG22" s="1">
@@ -1554,7 +1557,7 @@
       <c r="AE23" s="1">
         <v>0</v>
       </c>
-      <c r="BO23" s="1">
+      <c r="BP23" s="1">
         <v>0</v>
       </c>
       <c r="CG23" s="1">
@@ -1595,7 +1598,7 @@
       <c r="AE24" s="1">
         <v>0</v>
       </c>
-      <c r="BO24" s="1">
+      <c r="BP24" s="1">
         <v>4</v>
       </c>
       <c r="CG24" s="1">
@@ -1634,9 +1637,9 @@
         <v>0</v>
       </c>
       <c r="AE25" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO25" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP25" s="1">
         <v>0</v>
       </c>
       <c r="CG25" s="1">
@@ -1693,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="AF26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="1">
         <v>0</v>
@@ -1702,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ26" s="1">
         <v>0</v>
@@ -1711,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="AL26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM26" s="1">
         <v>0</v>
@@ -1720,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP26" s="1">
         <v>0</v>
@@ -1729,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="AR26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS26" s="1">
         <v>0</v>
@@ -1738,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV26" s="1">
         <v>0</v>
@@ -1747,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="AX26" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AY26" s="1">
         <v>0</v>
@@ -1756,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="BA26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB26" s="1">
         <v>0</v>
@@ -1765,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="BD26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE26" s="1">
         <v>0</v>
@@ -1774,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="BG26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BH26" s="1">
         <v>0</v>
@@ -1783,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="BJ26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK26" s="1">
         <v>0</v>
@@ -1792,12 +1795,15 @@
         <v>0</v>
       </c>
       <c r="BM26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BN26" s="1">
         <v>0</v>
       </c>
       <c r="BO26" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP26" s="1">
         <v>0</v>
       </c>
       <c r="CG26" s="1">
@@ -1853,7 +1859,7 @@
       <c r="AE27" s="1">
         <v>0</v>
       </c>
-      <c r="BO27" s="1">
+      <c r="BP27" s="1">
         <v>4</v>
       </c>
       <c r="CV27" s="1">
@@ -1886,9 +1892,9 @@
         <v>0</v>
       </c>
       <c r="AE28" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO28" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP28" s="1">
         <v>0</v>
       </c>
       <c r="CV28" s="1">
@@ -1970,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="AE31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV31" s="1">
         <v>0</v>
@@ -2060,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="AE34" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CM34" s="1">
         <v>4</v>
@@ -2159,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="AE37" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BW37" s="3">
         <v>0</v>
@@ -2264,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="AE40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BW40" s="3">
         <v>0</v>
@@ -2411,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="AE43" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN43" s="2">
         <v>0</v>
@@ -2714,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="AE46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN46" s="2">
         <v>0</v>
@@ -2898,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="AE48" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AN48" s="2">
         <v>0</v>
@@ -2990,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="AE49" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN49" s="2">
         <v>0</v>
@@ -3260,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="AE52" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN52" s="2">
         <v>0</v>
@@ -3527,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="AE55" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN55" s="2">
         <v>0</v>
@@ -3824,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="AE58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN58" s="2">
         <v>0</v>
@@ -4082,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="AE61" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN61" s="2">
         <v>0</v>
@@ -4250,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="AE64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO64" s="1">
         <v>0</v>
@@ -4358,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="AE67" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO67" s="1">
         <v>0</v>
@@ -4508,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="AE70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO70" s="1">
         <v>0</v>
@@ -4628,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="AE73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO73" s="1">
         <v>0</v>
@@ -4706,9 +4712,6 @@
       <c r="U75" s="1">
         <v>0</v>
       </c>
-      <c r="AE75" s="1">
-        <v>0</v>
-      </c>
       <c r="BO75" s="1">
         <v>4</v>
       </c>
@@ -4726,9 +4729,6 @@
       <c r="U76" s="1">
         <v>0</v>
       </c>
-      <c r="AE76" s="1">
-        <v>4</v>
-      </c>
       <c r="BO76" s="1">
         <v>0</v>
       </c>
@@ -4745,9 +4745,6 @@
       </c>
       <c r="U77" s="1">
         <v>4</v>
-      </c>
-      <c r="AE77" s="1">
-        <v>0</v>
       </c>
       <c r="BO77" s="1">
         <v>0</v>
